--- a/12_Equity_Finance/_template_BASE.xlsx
+++ b/12_Equity_Finance/_template_BASE.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="120">
   <si>
     <t xml:space="preserve">[TICKER] — Company Name</t>
   </si>
@@ -253,6 +253,9 @@
   </si>
   <si>
     <t xml:space="preserve">Total equity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Balance check (Total assets - Total liabilities - Total equity, should = 0)</t>
   </si>
   <si>
     <t xml:space="preserve">Cash Flow ($mm)</t>
@@ -556,116 +559,128 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="31">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -922,120 +937,120 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B2:D20"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="40"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="4"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="4" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="4" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="4" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="4" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="5" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="C11" s="5"/>
-      <c r="D11" s="5"/>
+      <c r="C11" s="6"/>
+      <c r="D11" s="6"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="5"/>
-      <c r="C12" s="5"/>
-      <c r="D12" s="5"/>
+      <c r="B12" s="6"/>
+      <c r="C12" s="6"/>
+      <c r="D12" s="6"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="5"/>
-      <c r="C13" s="5"/>
-      <c r="D13" s="5"/>
+      <c r="B13" s="6"/>
+      <c r="C13" s="6"/>
+      <c r="D13" s="6"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="5"/>
-      <c r="C14" s="5"/>
-      <c r="D14" s="5"/>
+      <c r="B14" s="6"/>
+      <c r="C14" s="6"/>
+      <c r="D14" s="6"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="2" t="s">
+      <c r="B16" s="3" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="3" t="s">
+      <c r="B17" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C17" s="4" t="s">
+      <c r="C17" s="5" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="4" t="s">
+      <c r="B18" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="C18" s="5" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="6" t="s">
+      <c r="B19" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="C19" s="4" t="s">
+      <c r="C19" s="5" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="7" t="s">
+      <c r="B20" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="C20" s="4" t="s">
+      <c r="C20" s="5" t="s">
         <v>18</v>
       </c>
     </row>
@@ -1059,270 +1074,270 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A2:H14"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="3" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="3" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="40"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="8"/>
-      <c r="B4" s="8" t="s">
+      <c r="A4" s="9"/>
+      <c r="B4" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C4" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="D4" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="E4" s="8" t="s">
+      <c r="E4" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="F4" s="8" t="s">
+      <c r="F4" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="G4" s="8" t="s">
+      <c r="G4" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="H4" s="8" t="s">
+      <c r="H4" s="9" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="C5" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" s="10" t="s">
+      <c r="C5" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="C6" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" s="10" t="s">
+      <c r="C6" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="C7" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" s="10" t="s">
+      <c r="C7" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C8" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" s="10" t="s">
+      <c r="C8" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="C9" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" s="10" t="s">
+      <c r="C9" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="C10" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" s="10" t="s">
+      <c r="C10" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="C11" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" s="10" t="s">
+      <c r="C11" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="C12" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" s="10" t="s">
+      <c r="C12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="4" t="s">
+      <c r="B13" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="C13" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" s="10" t="s">
+      <c r="C13" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="4" t="s">
+      <c r="B14" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="C14" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" s="10" t="s">
+      <c r="C14" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="11" t="s">
         <v>28</v>
       </c>
     </row>
@@ -1343,290 +1358,446 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A2:I20"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="3" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="3" style="1" width="13"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="8"/>
-      <c r="B4" s="8" t="s">
+      <c r="A4" s="9"/>
+      <c r="B4" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C4" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="D4" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="E4" s="8" t="s">
+      <c r="E4" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="F4" s="8" t="s">
+      <c r="F4" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="G4" s="8" t="s">
+      <c r="G4" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="H4" s="8" t="s">
+      <c r="H4" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="I4" s="8" t="s">
+      <c r="I4" s="9" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C5" s="13"/>
-      <c r="D5" s="13"/>
-      <c r="E5" s="13"/>
-      <c r="F5" s="13"/>
-      <c r="G5" s="13"/>
-      <c r="H5" s="13"/>
-      <c r="I5" s="13"/>
+      <c r="C5" s="14"/>
+      <c r="D5" s="14"/>
+      <c r="E5" s="14"/>
+      <c r="F5" s="14" t="n">
+        <f aca="false">E5*(1+Assumptions!C5)</f>
+        <v>0</v>
+      </c>
+      <c r="G5" s="14" t="n">
+        <f aca="false">F5*(1+Assumptions!D5)</f>
+        <v>0</v>
+      </c>
+      <c r="H5" s="14" t="n">
+        <f aca="false">G5*(1+Assumptions!E5)</f>
+        <v>0</v>
+      </c>
+      <c r="I5" s="14" t="n">
+        <f aca="false">H5*(1+Assumptions!F5)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="C6" s="14"/>
-      <c r="D6" s="14" t="str">
+      <c r="C6" s="15"/>
+      <c r="D6" s="15" t="str">
         <f aca="false">IFERROR(D5/C5-1,"-")</f>
         <v>-</v>
       </c>
-      <c r="E6" s="14" t="str">
+      <c r="E6" s="15" t="str">
         <f aca="false">IFERROR(E5/D5-1,"-")</f>
         <v>-</v>
       </c>
-      <c r="F6" s="14" t="str">
+      <c r="F6" s="15" t="str">
         <f aca="false">IFERROR(F5/E5-1,"-")</f>
         <v>-</v>
       </c>
-      <c r="G6" s="14" t="str">
+      <c r="G6" s="15" t="str">
         <f aca="false">IFERROR(G5/F5-1,"-")</f>
         <v>-</v>
       </c>
-      <c r="H6" s="14" t="str">
+      <c r="H6" s="15" t="str">
         <f aca="false">IFERROR(H5/G5-1,"-")</f>
         <v>-</v>
       </c>
-      <c r="I6" s="14" t="str">
+      <c r="I6" s="15" t="str">
         <f aca="false">IFERROR(I5/H5-1,"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="C7" s="13"/>
-      <c r="D7" s="13"/>
-      <c r="E7" s="13"/>
-      <c r="F7" s="13"/>
-      <c r="G7" s="13"/>
-      <c r="H7" s="13"/>
-      <c r="I7" s="13"/>
+      <c r="C7" s="14"/>
+      <c r="D7" s="14"/>
+      <c r="E7" s="14"/>
+      <c r="F7" s="14" t="n">
+        <f aca="false">F5*(1-Assumptions!C6)</f>
+        <v>0</v>
+      </c>
+      <c r="G7" s="14" t="n">
+        <f aca="false">G5*(1-Assumptions!D6)</f>
+        <v>0</v>
+      </c>
+      <c r="H7" s="14" t="n">
+        <f aca="false">H5*(1-Assumptions!E6)</f>
+        <v>0</v>
+      </c>
+      <c r="I7" s="14" t="n">
+        <f aca="false">I5*(1-Assumptions!F6)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="C8" s="13"/>
-      <c r="D8" s="13" t="n">
+      <c r="C8" s="14"/>
+      <c r="D8" s="14" t="n">
         <f aca="false">D5-D7</f>
         <v>0</v>
       </c>
-      <c r="E8" s="13" t="n">
+      <c r="E8" s="14" t="n">
         <f aca="false">E5-E7</f>
         <v>0</v>
       </c>
-      <c r="F8" s="13" t="n">
+      <c r="F8" s="14" t="n">
         <f aca="false">F5-F7</f>
         <v>0</v>
       </c>
-      <c r="G8" s="13" t="n">
+      <c r="G8" s="14" t="n">
         <f aca="false">G5-G7</f>
         <v>0</v>
       </c>
-      <c r="H8" s="13" t="n">
+      <c r="H8" s="14" t="n">
         <f aca="false">H5-H7</f>
         <v>0</v>
       </c>
-      <c r="I8" s="13" t="n">
+      <c r="I8" s="14" t="n">
         <f aca="false">I5-I7</f>
         <v>0</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="C9" s="14"/>
-      <c r="D9" s="14" t="str">
+      <c r="C9" s="15"/>
+      <c r="D9" s="15" t="str">
         <f aca="false">IFERROR(D8/D5,"-")</f>
         <v>-</v>
       </c>
-      <c r="E9" s="14" t="str">
+      <c r="E9" s="15" t="str">
         <f aca="false">IFERROR(E8/E5,"-")</f>
         <v>-</v>
       </c>
-      <c r="F9" s="14" t="str">
+      <c r="F9" s="15" t="str">
         <f aca="false">IFERROR(F8/F5,"-")</f>
         <v>-</v>
       </c>
-      <c r="G9" s="14" t="str">
+      <c r="G9" s="15" t="str">
         <f aca="false">IFERROR(G8/G5,"-")</f>
         <v>-</v>
       </c>
-      <c r="H9" s="14" t="str">
+      <c r="H9" s="15" t="str">
         <f aca="false">IFERROR(H8/H5,"-")</f>
         <v>-</v>
       </c>
-      <c r="I9" s="14" t="str">
+      <c r="I9" s="15" t="str">
         <f aca="false">IFERROR(I8/I5,"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="C10" s="13"/>
-      <c r="D10" s="13"/>
-      <c r="E10" s="13"/>
-      <c r="F10" s="13"/>
-      <c r="G10" s="13"/>
-      <c r="H10" s="13"/>
-      <c r="I10" s="13"/>
+      <c r="C10" s="14"/>
+      <c r="D10" s="14"/>
+      <c r="E10" s="14"/>
+      <c r="F10" s="14" t="n">
+        <f aca="false">F5*Assumptions!C7</f>
+        <v>0</v>
+      </c>
+      <c r="G10" s="14" t="n">
+        <f aca="false">G5*Assumptions!D7</f>
+        <v>0</v>
+      </c>
+      <c r="H10" s="14" t="n">
+        <f aca="false">H5*Assumptions!E7</f>
+        <v>0</v>
+      </c>
+      <c r="I10" s="14" t="n">
+        <f aca="false">I5*Assumptions!F7</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="C11" s="13"/>
-      <c r="D11" s="13"/>
-      <c r="E11" s="13"/>
-      <c r="F11" s="13"/>
-      <c r="G11" s="13"/>
-      <c r="H11" s="13"/>
-      <c r="I11" s="13"/>
+      <c r="C11" s="14"/>
+      <c r="D11" s="14"/>
+      <c r="E11" s="14"/>
+      <c r="F11" s="14" t="n">
+        <f aca="false">F8-F10</f>
+        <v>0</v>
+      </c>
+      <c r="G11" s="14" t="n">
+        <f aca="false">G8-G10</f>
+        <v>0</v>
+      </c>
+      <c r="H11" s="14" t="n">
+        <f aca="false">H8-H10</f>
+        <v>0</v>
+      </c>
+      <c r="I11" s="14" t="n">
+        <f aca="false">I8-I10</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="C12" s="14"/>
-      <c r="D12" s="14"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="14"/>
-      <c r="G12" s="14"/>
-      <c r="H12" s="14"/>
-      <c r="I12" s="14"/>
+      <c r="C12" s="15"/>
+      <c r="D12" s="15"/>
+      <c r="E12" s="15"/>
+      <c r="F12" s="15" t="str">
+        <f aca="false">IFERROR(F11/F5,"-")</f>
+        <v>-</v>
+      </c>
+      <c r="G12" s="15" t="str">
+        <f aca="false">IFERROR(G11/G5,"-")</f>
+        <v>-</v>
+      </c>
+      <c r="H12" s="15" t="str">
+        <f aca="false">IFERROR(H11/H5,"-")</f>
+        <v>-</v>
+      </c>
+      <c r="I12" s="15" t="str">
+        <f aca="false">IFERROR(I11/I5,"-")</f>
+        <v>-</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="4" t="s">
+      <c r="B13" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="C13" s="13"/>
-      <c r="D13" s="13"/>
-      <c r="E13" s="13"/>
-      <c r="F13" s="13"/>
-      <c r="G13" s="13"/>
-      <c r="H13" s="13"/>
-      <c r="I13" s="13"/>
+      <c r="C13" s="14"/>
+      <c r="D13" s="14"/>
+      <c r="E13" s="14"/>
+      <c r="F13" s="14" t="n">
+        <f aca="false">F5*Assumptions!C10*Assumptions!C9</f>
+        <v>0</v>
+      </c>
+      <c r="G13" s="14" t="n">
+        <f aca="false">G5*Assumptions!D10*Assumptions!D9</f>
+        <v>0</v>
+      </c>
+      <c r="H13" s="14" t="n">
+        <f aca="false">H5*Assumptions!E10*Assumptions!E9</f>
+        <v>0</v>
+      </c>
+      <c r="I13" s="14" t="n">
+        <f aca="false">I5*Assumptions!F10*Assumptions!F9</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="2" t="s">
+      <c r="B14" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="C14" s="13"/>
-      <c r="D14" s="13"/>
-      <c r="E14" s="13"/>
-      <c r="F14" s="13"/>
-      <c r="G14" s="13"/>
-      <c r="H14" s="13"/>
-      <c r="I14" s="13"/>
+      <c r="C14" s="14"/>
+      <c r="D14" s="14"/>
+      <c r="E14" s="14"/>
+      <c r="F14" s="14" t="n">
+        <f aca="false">F11-F13</f>
+        <v>0</v>
+      </c>
+      <c r="G14" s="14" t="n">
+        <f aca="false">G11-G13</f>
+        <v>0</v>
+      </c>
+      <c r="H14" s="14" t="n">
+        <f aca="false">H11-H13</f>
+        <v>0</v>
+      </c>
+      <c r="I14" s="14" t="n">
+        <f aca="false">I11-I13</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="4" t="s">
+      <c r="B15" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="C15" s="13"/>
-      <c r="D15" s="13"/>
-      <c r="E15" s="13"/>
-      <c r="F15" s="13"/>
-      <c r="G15" s="13"/>
-      <c r="H15" s="13"/>
-      <c r="I15" s="13"/>
+      <c r="C15" s="14"/>
+      <c r="D15" s="14"/>
+      <c r="E15" s="14"/>
+      <c r="F15" s="14" t="n">
+        <f aca="false">$E$15</f>
+        <v>0</v>
+      </c>
+      <c r="G15" s="14" t="n">
+        <f aca="false">$E$15</f>
+        <v>0</v>
+      </c>
+      <c r="H15" s="14" t="n">
+        <f aca="false">$E$15</f>
+        <v>0</v>
+      </c>
+      <c r="I15" s="14" t="n">
+        <f aca="false">$E$15</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="4" t="s">
+      <c r="B16" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="C16" s="13"/>
-      <c r="D16" s="13"/>
-      <c r="E16" s="13"/>
-      <c r="F16" s="13"/>
-      <c r="G16" s="13"/>
-      <c r="H16" s="13"/>
-      <c r="I16" s="13"/>
+      <c r="C16" s="14"/>
+      <c r="D16" s="14"/>
+      <c r="E16" s="14"/>
+      <c r="F16" s="14" t="n">
+        <f aca="false">F14-F15</f>
+        <v>0</v>
+      </c>
+      <c r="G16" s="14" t="n">
+        <f aca="false">G14-G15</f>
+        <v>0</v>
+      </c>
+      <c r="H16" s="14" t="n">
+        <f aca="false">H14-H15</f>
+        <v>0</v>
+      </c>
+      <c r="I16" s="14" t="n">
+        <f aca="false">I14-I15</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="4" t="s">
+      <c r="B17" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="C17" s="13"/>
-      <c r="D17" s="13"/>
-      <c r="E17" s="13"/>
-      <c r="F17" s="13"/>
-      <c r="G17" s="13"/>
-      <c r="H17" s="13"/>
-      <c r="I17" s="13"/>
+      <c r="C17" s="14"/>
+      <c r="D17" s="14"/>
+      <c r="E17" s="14"/>
+      <c r="F17" s="14" t="n">
+        <f aca="false">F16*Assumptions!C8</f>
+        <v>0</v>
+      </c>
+      <c r="G17" s="14" t="n">
+        <f aca="false">G16*Assumptions!D8</f>
+        <v>0</v>
+      </c>
+      <c r="H17" s="14" t="n">
+        <f aca="false">H16*Assumptions!E8</f>
+        <v>0</v>
+      </c>
+      <c r="I17" s="14" t="n">
+        <f aca="false">I16*Assumptions!F8</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="2" t="s">
+      <c r="B18" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="C18" s="13"/>
-      <c r="D18" s="13"/>
-      <c r="E18" s="13"/>
-      <c r="F18" s="13"/>
-      <c r="G18" s="13"/>
-      <c r="H18" s="13"/>
-      <c r="I18" s="13"/>
+      <c r="C18" s="14"/>
+      <c r="D18" s="14"/>
+      <c r="E18" s="14"/>
+      <c r="F18" s="14" t="n">
+        <f aca="false">F16-F17</f>
+        <v>0</v>
+      </c>
+      <c r="G18" s="14" t="n">
+        <f aca="false">G16-G17</f>
+        <v>0</v>
+      </c>
+      <c r="H18" s="14" t="n">
+        <f aca="false">H16-H17</f>
+        <v>0</v>
+      </c>
+      <c r="I18" s="14" t="n">
+        <f aca="false">I16-I17</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="4" t="s">
+      <c r="B19" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="C19" s="13"/>
-      <c r="D19" s="13"/>
-      <c r="E19" s="13"/>
-      <c r="F19" s="13"/>
-      <c r="G19" s="13"/>
-      <c r="H19" s="13"/>
-      <c r="I19" s="13"/>
+      <c r="C19" s="14"/>
+      <c r="D19" s="14"/>
+      <c r="E19" s="14"/>
+      <c r="F19" s="14" t="n">
+        <f aca="false">Assumptions!C12</f>
+        <v>0</v>
+      </c>
+      <c r="G19" s="14" t="n">
+        <f aca="false">Assumptions!D12</f>
+        <v>0</v>
+      </c>
+      <c r="H19" s="14" t="n">
+        <f aca="false">Assumptions!E12</f>
+        <v>0</v>
+      </c>
+      <c r="I19" s="14" t="n">
+        <f aca="false">Assumptions!F12</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="4" t="s">
+      <c r="B20" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="C20" s="13"/>
-      <c r="D20" s="13"/>
-      <c r="E20" s="13"/>
-      <c r="F20" s="13"/>
-      <c r="G20" s="13"/>
-      <c r="H20" s="13"/>
-      <c r="I20" s="13"/>
+      <c r="C20" s="14"/>
+      <c r="D20" s="14"/>
+      <c r="E20" s="14"/>
+      <c r="F20" s="14" t="str">
+        <f aca="false">IFERROR(F18/F19,"-")</f>
+        <v>-</v>
+      </c>
+      <c r="G20" s="14" t="str">
+        <f aca="false">IFERROR(G18/G19,"-")</f>
+        <v>-</v>
+      </c>
+      <c r="H20" s="14" t="str">
+        <f aca="false">IFERROR(H18/H19,"-")</f>
+        <v>-</v>
+      </c>
+      <c r="I20" s="14" t="str">
+        <f aca="false">IFERROR(I18/I19,"-")</f>
+        <v>-</v>
+      </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -1644,169 +1815,254 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A2:G17"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A2:G19"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="3" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="3" style="1" width="13"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="8"/>
-      <c r="B4" s="8" t="s">
+      <c r="A4" s="9"/>
+      <c r="B4" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C4" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="D4" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="E4" s="8" t="s">
+      <c r="E4" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="F4" s="8" t="s">
+      <c r="F4" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="G4" s="15" t="s">
+      <c r="G4" s="16" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="C5" s="13"/>
-      <c r="D5" s="13"/>
-      <c r="E5" s="13"/>
-      <c r="F5" s="13"/>
-      <c r="G5" s="13"/>
+      <c r="C5" s="14"/>
+      <c r="D5" s="14"/>
+      <c r="E5" s="14"/>
+      <c r="F5" s="14"/>
+      <c r="G5" s="14"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="C6" s="13"/>
-      <c r="D6" s="13"/>
-      <c r="E6" s="13"/>
-      <c r="F6" s="13"/>
-      <c r="G6" s="13"/>
+      <c r="C6" s="14"/>
+      <c r="D6" s="14"/>
+      <c r="E6" s="14"/>
+      <c r="F6" s="14"/>
+      <c r="G6" s="14"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="C7" s="13"/>
-      <c r="D7" s="13"/>
-      <c r="E7" s="13"/>
-      <c r="F7" s="13"/>
-      <c r="G7" s="13"/>
+      <c r="C7" s="14"/>
+      <c r="D7" s="14"/>
+      <c r="E7" s="14"/>
+      <c r="F7" s="14"/>
+      <c r="G7" s="14"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="C8" s="13"/>
-      <c r="D8" s="13"/>
-      <c r="E8" s="13"/>
-      <c r="F8" s="13"/>
-      <c r="G8" s="13"/>
+      <c r="C8" s="14" t="n">
+        <f aca="false">C5+C6+C7</f>
+        <v>0</v>
+      </c>
+      <c r="D8" s="14" t="n">
+        <f aca="false">D5+D6+D7</f>
+        <v>0</v>
+      </c>
+      <c r="E8" s="14" t="n">
+        <f aca="false">E5+E6+E7</f>
+        <v>0</v>
+      </c>
+      <c r="F8" s="14" t="n">
+        <f aca="false">F5+F6+F7</f>
+        <v>0</v>
+      </c>
+      <c r="G8" s="14" t="n">
+        <f aca="false">G5+G6+G7</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="C9" s="13"/>
-      <c r="D9" s="13"/>
-      <c r="E9" s="13"/>
-      <c r="F9" s="13"/>
-      <c r="G9" s="13"/>
+      <c r="C9" s="14"/>
+      <c r="D9" s="14"/>
+      <c r="E9" s="14"/>
+      <c r="F9" s="14"/>
+      <c r="G9" s="14"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="C10" s="13"/>
-      <c r="D10" s="13"/>
-      <c r="E10" s="13"/>
-      <c r="F10" s="13"/>
-      <c r="G10" s="13"/>
+      <c r="C10" s="14"/>
+      <c r="D10" s="14"/>
+      <c r="E10" s="14"/>
+      <c r="F10" s="14"/>
+      <c r="G10" s="14"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="C11" s="13"/>
-      <c r="D11" s="13"/>
-      <c r="E11" s="13"/>
-      <c r="F11" s="13"/>
-      <c r="G11" s="13"/>
+      <c r="C11" s="14" t="n">
+        <f aca="false">C8+C9+C10</f>
+        <v>0</v>
+      </c>
+      <c r="D11" s="14" t="n">
+        <f aca="false">D8+D9+D10</f>
+        <v>0</v>
+      </c>
+      <c r="E11" s="14" t="n">
+        <f aca="false">E8+E9+E10</f>
+        <v>0</v>
+      </c>
+      <c r="F11" s="14" t="n">
+        <f aca="false">F8+F9+F10</f>
+        <v>0</v>
+      </c>
+      <c r="G11" s="14" t="n">
+        <f aca="false">G8+G9+G10</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="C12" s="13"/>
-      <c r="D12" s="13"/>
-      <c r="E12" s="13"/>
-      <c r="F12" s="13"/>
-      <c r="G12" s="13"/>
+      <c r="C12" s="14"/>
+      <c r="D12" s="14"/>
+      <c r="E12" s="14"/>
+      <c r="F12" s="14"/>
+      <c r="G12" s="14"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="4" t="s">
+      <c r="B13" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="C13" s="13"/>
-      <c r="D13" s="13"/>
-      <c r="E13" s="13"/>
-      <c r="F13" s="13"/>
-      <c r="G13" s="13"/>
+      <c r="C13" s="14"/>
+      <c r="D13" s="14"/>
+      <c r="E13" s="14"/>
+      <c r="F13" s="14"/>
+      <c r="G13" s="14"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="2" t="s">
+      <c r="B14" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="C14" s="13"/>
-      <c r="D14" s="13"/>
-      <c r="E14" s="13"/>
-      <c r="F14" s="13"/>
-      <c r="G14" s="13"/>
+      <c r="C14" s="14" t="n">
+        <f aca="false">C12+C13</f>
+        <v>0</v>
+      </c>
+      <c r="D14" s="14" t="n">
+        <f aca="false">D12+D13</f>
+        <v>0</v>
+      </c>
+      <c r="E14" s="14" t="n">
+        <f aca="false">E12+E13</f>
+        <v>0</v>
+      </c>
+      <c r="F14" s="14" t="n">
+        <f aca="false">F12+F13</f>
+        <v>0</v>
+      </c>
+      <c r="G14" s="14" t="n">
+        <f aca="false">G12+G13</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="4" t="s">
+      <c r="B15" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="C15" s="13"/>
-      <c r="D15" s="13"/>
-      <c r="E15" s="13"/>
-      <c r="F15" s="13"/>
-      <c r="G15" s="13"/>
+      <c r="C15" s="14"/>
+      <c r="D15" s="14"/>
+      <c r="E15" s="14"/>
+      <c r="F15" s="14"/>
+      <c r="G15" s="14"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="2" t="s">
+      <c r="B16" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="C16" s="13"/>
-      <c r="D16" s="13"/>
-      <c r="E16" s="13"/>
-      <c r="F16" s="13"/>
-      <c r="G16" s="13"/>
+      <c r="C16" s="14" t="n">
+        <f aca="false">C14+C15</f>
+        <v>0</v>
+      </c>
+      <c r="D16" s="14" t="n">
+        <f aca="false">D14+D15</f>
+        <v>0</v>
+      </c>
+      <c r="E16" s="14" t="n">
+        <f aca="false">E14+E15</f>
+        <v>0</v>
+      </c>
+      <c r="F16" s="14" t="n">
+        <f aca="false">F14+F15</f>
+        <v>0</v>
+      </c>
+      <c r="G16" s="14" t="n">
+        <f aca="false">G14+G15</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="2" t="s">
+      <c r="B17" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="C17" s="13"/>
-      <c r="D17" s="13"/>
-      <c r="E17" s="13"/>
-      <c r="F17" s="13"/>
-      <c r="G17" s="13"/>
+      <c r="C17" s="14"/>
+      <c r="D17" s="14"/>
+      <c r="E17" s="14"/>
+      <c r="F17" s="14"/>
+      <c r="G17" s="14"/>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B19" s="17" t="s">
+        <v>75</v>
+      </c>
+      <c r="C19" s="18" t="n">
+        <f aca="false">C11-C16-C17</f>
+        <v>0</v>
+      </c>
+      <c r="D19" s="18" t="n">
+        <f aca="false">D11-D16-D17</f>
+        <v>0</v>
+      </c>
+      <c r="E19" s="18" t="n">
+        <f aca="false">E11-E16-E17</f>
+        <v>0</v>
+      </c>
+      <c r="F19" s="18" t="n">
+        <f aca="false">F11-F16-F17</f>
+        <v>0</v>
+      </c>
+      <c r="G19" s="18" t="n">
+        <f aca="false">G11-G16-G17</f>
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -1825,128 +2081,191 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A2:G13"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="3" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="3" style="1" width="13"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="1" t="s">
-        <v>75</v>
+      <c r="B2" s="2" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="8"/>
-      <c r="B4" s="8" t="s">
+      <c r="A4" s="9"/>
+      <c r="B4" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C4" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="D4" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="E4" s="8" t="s">
+      <c r="E4" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="F4" s="8" t="s">
+      <c r="F4" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="G4" s="15" t="s">
+      <c r="G4" s="16" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="C5" s="13"/>
-      <c r="D5" s="13"/>
-      <c r="E5" s="13"/>
-      <c r="F5" s="13"/>
-      <c r="G5" s="13"/>
+      <c r="C5" s="14"/>
+      <c r="D5" s="14"/>
+      <c r="E5" s="19" t="n">
+        <f aca="false">IS!F18</f>
+        <v>0</v>
+      </c>
+      <c r="F5" s="19" t="n">
+        <f aca="false">IS!G18</f>
+        <v>0</v>
+      </c>
+      <c r="G5" s="19" t="n">
+        <f aca="false">IS!H18</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="C6" s="13"/>
-      <c r="D6" s="13"/>
-      <c r="E6" s="13"/>
-      <c r="F6" s="13"/>
-      <c r="G6" s="13"/>
+      <c r="B6" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="C6" s="14"/>
+      <c r="D6" s="14"/>
+      <c r="E6" s="19" t="n">
+        <f aca="false">IS!F13</f>
+        <v>0</v>
+      </c>
+      <c r="F6" s="19" t="n">
+        <f aca="false">IS!G13</f>
+        <v>0</v>
+      </c>
+      <c r="G6" s="19" t="n">
+        <f aca="false">IS!H13</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="C7" s="13"/>
-      <c r="D7" s="13"/>
-      <c r="E7" s="13"/>
-      <c r="F7" s="13"/>
-      <c r="G7" s="13"/>
+      <c r="B7" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="C7" s="14"/>
+      <c r="D7" s="14"/>
+      <c r="E7" s="14"/>
+      <c r="F7" s="14"/>
+      <c r="G7" s="14"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="C8" s="13"/>
-      <c r="D8" s="13"/>
-      <c r="E8" s="13"/>
-      <c r="F8" s="13"/>
-      <c r="G8" s="13"/>
+      <c r="B8" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="C8" s="14" t="n">
+        <f aca="false">C5+C6+C7</f>
+        <v>0</v>
+      </c>
+      <c r="D8" s="14" t="n">
+        <f aca="false">D5+D6+D7</f>
+        <v>0</v>
+      </c>
+      <c r="E8" s="14" t="n">
+        <f aca="false">E5+E6+E7</f>
+        <v>0</v>
+      </c>
+      <c r="F8" s="14" t="n">
+        <f aca="false">F5+F6+F7</f>
+        <v>0</v>
+      </c>
+      <c r="G8" s="14" t="n">
+        <f aca="false">G5+G6+G7</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="C9" s="13"/>
-      <c r="D9" s="13"/>
-      <c r="E9" s="13"/>
-      <c r="F9" s="13"/>
-      <c r="G9" s="13"/>
+      <c r="B9" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="C9" s="14"/>
+      <c r="D9" s="14"/>
+      <c r="E9" s="14"/>
+      <c r="F9" s="14"/>
+      <c r="G9" s="14"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="C10" s="13"/>
-      <c r="D10" s="13"/>
-      <c r="E10" s="13"/>
-      <c r="F10" s="13"/>
-      <c r="G10" s="13"/>
+      <c r="B10" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C10" s="14" t="n">
+        <f aca="false">C8+C9</f>
+        <v>0</v>
+      </c>
+      <c r="D10" s="14" t="n">
+        <f aca="false">D8+D9</f>
+        <v>0</v>
+      </c>
+      <c r="E10" s="14" t="n">
+        <f aca="false">E8+E9</f>
+        <v>0</v>
+      </c>
+      <c r="F10" s="14" t="n">
+        <f aca="false">F8+F9</f>
+        <v>0</v>
+      </c>
+      <c r="G10" s="14" t="n">
+        <f aca="false">G8+G9</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="C11" s="13"/>
-      <c r="D11" s="13"/>
-      <c r="E11" s="13"/>
-      <c r="F11" s="13"/>
-      <c r="G11" s="13"/>
+      <c r="B11" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="C11" s="14"/>
+      <c r="D11" s="14"/>
+      <c r="E11" s="14"/>
+      <c r="F11" s="14"/>
+      <c r="G11" s="14"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="C12" s="13"/>
-      <c r="D12" s="13"/>
-      <c r="E12" s="13"/>
-      <c r="F12" s="13"/>
-      <c r="G12" s="13"/>
+      <c r="B12" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="C12" s="14"/>
+      <c r="D12" s="14"/>
+      <c r="E12" s="14"/>
+      <c r="F12" s="14"/>
+      <c r="G12" s="14"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="C13" s="13"/>
-      <c r="D13" s="13"/>
-      <c r="E13" s="13"/>
-      <c r="F13" s="13"/>
-      <c r="G13" s="13"/>
+      <c r="B13" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="C13" s="14" t="n">
+        <f aca="false">C10+C11+C12</f>
+        <v>0</v>
+      </c>
+      <c r="D13" s="14" t="n">
+        <f aca="false">D10+D11+D12</f>
+        <v>0</v>
+      </c>
+      <c r="E13" s="14" t="n">
+        <f aca="false">E10+E11+E12</f>
+        <v>0</v>
+      </c>
+      <c r="F13" s="14" t="n">
+        <f aca="false">F10+F11+F12</f>
+        <v>0</v>
+      </c>
+      <c r="G13" s="14" t="n">
+        <f aca="false">G10+G11+G12</f>
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -1965,177 +2284,192 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B2:I14"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="3" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="3" style="1" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="14"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="1" t="s">
-        <v>84</v>
+      <c r="B2" s="2" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C4" s="8" t="s">
+      <c r="C4" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="D4" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="E4" s="8" t="s">
+      <c r="E4" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="F4" s="8" t="s">
+      <c r="F4" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="G4" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="H4" s="2" t="s">
+      <c r="G4" s="9" t="s">
         <v>86</v>
       </c>
+      <c r="H4" s="3" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="0" t="s">
-        <v>87</v>
-      </c>
-      <c r="C5" s="16"/>
-      <c r="D5" s="16"/>
-      <c r="E5" s="16"/>
-      <c r="F5" s="16"/>
-      <c r="G5" s="16"/>
-      <c r="H5" s="15" t="s">
+      <c r="B5" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="I5" s="17" t="n">
+      <c r="C5" s="20" t="n">
+        <f aca="false">IS!F14*(1-Assumptions!C8)+IS!F13-IS!F5*Assumptions!C10</f>
+        <v>0</v>
+      </c>
+      <c r="D5" s="20" t="n">
+        <f aca="false">IS!G14*(1-Assumptions!D8)+IS!G13-IS!G5*Assumptions!D10</f>
+        <v>0</v>
+      </c>
+      <c r="E5" s="20" t="n">
+        <f aca="false">IS!H14*(1-Assumptions!E8)+IS!H13-IS!H5*Assumptions!E10</f>
+        <v>0</v>
+      </c>
+      <c r="F5" s="20" t="n">
+        <f aca="false">IS!I14*(1-Assumptions!F8)+IS!I13-IS!I5*Assumptions!F10</f>
+        <v>0</v>
+      </c>
+      <c r="G5" s="20" t="n">
+        <f aca="false">F5*(1+Assumptions!G5)</f>
+        <v>0</v>
+      </c>
+      <c r="H5" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="I5" s="21" t="n">
         <v>0.1</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="0" t="s">
-        <v>89</v>
-      </c>
-      <c r="C6" s="18" t="n">
+      <c r="B6" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C6" s="22" t="n">
         <f aca="false">1/(1+$I$5)^(1)</f>
         <v>0.909090909090909</v>
       </c>
-      <c r="D6" s="18" t="n">
+      <c r="D6" s="22" t="n">
         <f aca="false">1/(1+$I$5)^(2)</f>
         <v>0.826446280991735</v>
       </c>
-      <c r="E6" s="18" t="n">
+      <c r="E6" s="22" t="n">
         <f aca="false">1/(1+$I$5)^(3)</f>
         <v>0.751314800901578</v>
       </c>
-      <c r="F6" s="18" t="n">
+      <c r="F6" s="22" t="n">
         <f aca="false">1/(1+$I$5)^(4)</f>
         <v>0.683013455365071</v>
       </c>
-      <c r="G6" s="18" t="n">
+      <c r="G6" s="22" t="n">
         <f aca="false">1/(1+$I$5)^(5)</f>
         <v>0.620921323059155</v>
       </c>
-      <c r="H6" s="15" t="s">
-        <v>90</v>
-      </c>
-      <c r="I6" s="17" t="n">
+      <c r="H6" s="16" t="s">
+        <v>91</v>
+      </c>
+      <c r="I6" s="21" t="n">
         <v>0.025</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="0" t="s">
-        <v>91</v>
-      </c>
-      <c r="C7" s="19" t="n">
+      <c r="B7" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C7" s="23" t="n">
         <f aca="false">C5*C6</f>
         <v>0</v>
       </c>
-      <c r="D7" s="19" t="n">
+      <c r="D7" s="23" t="n">
         <f aca="false">D5*D6</f>
         <v>0</v>
       </c>
-      <c r="E7" s="19" t="n">
+      <c r="E7" s="23" t="n">
         <f aca="false">E5*E6</f>
         <v>0</v>
       </c>
-      <c r="F7" s="19" t="n">
+      <c r="F7" s="23" t="n">
         <f aca="false">F5*F6</f>
         <v>0</v>
       </c>
-      <c r="G7" s="19" t="n">
+      <c r="G7" s="23" t="n">
         <f aca="false">G5*G6</f>
         <v>0</v>
       </c>
-      <c r="H7" s="15" t="s">
-        <v>92</v>
-      </c>
-      <c r="I7" s="19" t="n">
+      <c r="H7" s="16" t="s">
+        <v>93</v>
+      </c>
+      <c r="I7" s="23" t="n">
         <f aca="false">G5*(1+I6)/(I5-I6)</f>
         <v>0</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H8" s="0" t="s">
-        <v>93</v>
-      </c>
-      <c r="I8" s="19" t="n">
+      <c r="H8" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="I8" s="23" t="n">
         <f aca="false">I7*G6</f>
         <v>0</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H9" s="0" t="s">
-        <v>94</v>
-      </c>
-      <c r="I9" s="19" t="n">
+      <c r="H9" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="I9" s="23" t="n">
         <f aca="false">SUM(C7:G7)</f>
         <v>0</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H10" s="0" t="s">
-        <v>95</v>
-      </c>
-      <c r="I10" s="20" t="n">
+      <c r="H10" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="I10" s="24" t="n">
         <f aca="false">I8+I9</f>
         <v>0</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H11" s="0" t="s">
-        <v>96</v>
-      </c>
-      <c r="I11" s="21" t="n">
+      <c r="H11" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="I11" s="25" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H12" s="0" t="s">
-        <v>97</v>
-      </c>
-      <c r="I12" s="20" t="n">
+      <c r="H12" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="I12" s="24" t="n">
         <f aca="false">I10-I11</f>
         <v>0</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H13" s="0" t="s">
-        <v>98</v>
-      </c>
-      <c r="I13" s="21" t="n">
+      <c r="H13" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="I13" s="25" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H14" s="0" t="s">
-        <v>99</v>
-      </c>
-      <c r="I14" s="20" t="n">
+      <c r="H14" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="I14" s="24" t="n">
         <f aca="false">I12/I13</f>
         <v>0</v>
       </c>
@@ -2157,228 +2491,228 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A2:H13"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="3" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="3" style="1" width="12"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="1" t="s">
-        <v>100</v>
+      <c r="B2" s="2" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="8"/>
-      <c r="B4" s="8" t="s">
-        <v>101</v>
-      </c>
-      <c r="C4" s="8" t="s">
+      <c r="A4" s="9"/>
+      <c r="B4" s="9" t="s">
         <v>102</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="C4" s="9" t="s">
         <v>103</v>
       </c>
-      <c r="E4" s="8" t="s">
+      <c r="D4" s="9" t="s">
         <v>104</v>
       </c>
-      <c r="F4" s="8" t="s">
+      <c r="E4" s="9" t="s">
         <v>105</v>
       </c>
-      <c r="G4" s="8" t="s">
+      <c r="F4" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="H4" s="8" t="s">
+      <c r="G4" s="9" t="s">
         <v>107</v>
       </c>
+      <c r="H4" s="9" t="s">
+        <v>108</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="C5" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" s="22" t="n">
+      <c r="B5" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="C5" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="26" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="C6" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" s="22" t="n">
+      <c r="B6" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="C6" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="26" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="C7" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" s="22" t="n">
+      <c r="B7" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="C7" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="26" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="C8" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" s="22" t="n">
+      <c r="B8" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="C8" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="26" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="C9" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" s="22" t="n">
+      <c r="B9" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="C9" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="26" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="C10" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" s="22" t="n">
+      <c r="B10" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="C10" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="26" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="C11" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" s="22" t="n">
+      <c r="B11" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="C11" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="26" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="C13" s="20" t="n">
+      <c r="B13" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="C13" s="24" t="n">
         <f aca="false">MEDIAN(C5:C12)</f>
         <v>0</v>
       </c>
-      <c r="D13" s="20" t="n">
+      <c r="D13" s="24" t="n">
         <f aca="false">MEDIAN(D5:D12)</f>
         <v>0</v>
       </c>
-      <c r="E13" s="20" t="n">
+      <c r="E13" s="24" t="n">
         <f aca="false">MEDIAN(E5:E12)</f>
         <v>0</v>
       </c>
-      <c r="F13" s="23" t="n">
+      <c r="F13" s="27" t="n">
         <f aca="false">MEDIAN(F5:F12)</f>
         <v>0</v>
       </c>
-      <c r="G13" s="23" t="n">
+      <c r="G13" s="27" t="n">
         <f aca="false">MEDIAN(G5:G12)</f>
         <v>0</v>
       </c>
-      <c r="H13" s="23" t="n">
+      <c r="H13" s="27" t="n">
         <f aca="false">MEDIAN(H5:H12)</f>
         <v>0</v>
       </c>
@@ -2400,136 +2734,136 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B2:G9"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="3" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="3" style="1" width="12"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="1" t="s">
-        <v>110</v>
+      <c r="B2" s="2" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="24" t="s">
-        <v>111</v>
-      </c>
-      <c r="C4" s="25" t="n">
+      <c r="B4" s="28" t="s">
+        <v>112</v>
+      </c>
+      <c r="C4" s="29" t="n">
         <v>0.015</v>
       </c>
-      <c r="D4" s="25" t="n">
+      <c r="D4" s="29" t="n">
         <v>0.02</v>
       </c>
-      <c r="E4" s="25" t="n">
+      <c r="E4" s="29" t="n">
         <v>0.025</v>
       </c>
-      <c r="F4" s="25" t="n">
+      <c r="F4" s="29" t="n">
         <v>0.03</v>
       </c>
-      <c r="G4" s="25" t="n">
+      <c r="G4" s="29" t="n">
         <v>0.035</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="25" t="n">
+      <c r="B5" s="29" t="n">
         <v>0.08</v>
       </c>
-      <c r="C5" s="26" t="s">
-        <v>112</v>
-      </c>
-      <c r="D5" s="26" t="s">
-        <v>112</v>
-      </c>
-      <c r="E5" s="26" t="s">
-        <v>112</v>
-      </c>
-      <c r="F5" s="26" t="s">
-        <v>112</v>
-      </c>
-      <c r="G5" s="26" t="s">
-        <v>112</v>
+      <c r="C5" s="17" t="s">
+        <v>113</v>
+      </c>
+      <c r="D5" s="17" t="s">
+        <v>113</v>
+      </c>
+      <c r="E5" s="17" t="s">
+        <v>113</v>
+      </c>
+      <c r="F5" s="17" t="s">
+        <v>113</v>
+      </c>
+      <c r="G5" s="17" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="25" t="n">
+      <c r="B6" s="29" t="n">
         <v>0.09</v>
       </c>
-      <c r="C6" s="26" t="s">
-        <v>112</v>
-      </c>
-      <c r="D6" s="26" t="s">
-        <v>112</v>
-      </c>
-      <c r="E6" s="26" t="s">
-        <v>112</v>
-      </c>
-      <c r="F6" s="26" t="s">
-        <v>112</v>
-      </c>
-      <c r="G6" s="26" t="s">
-        <v>112</v>
+      <c r="C6" s="17" t="s">
+        <v>113</v>
+      </c>
+      <c r="D6" s="17" t="s">
+        <v>113</v>
+      </c>
+      <c r="E6" s="17" t="s">
+        <v>113</v>
+      </c>
+      <c r="F6" s="17" t="s">
+        <v>113</v>
+      </c>
+      <c r="G6" s="17" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="25" t="n">
+      <c r="B7" s="29" t="n">
         <v>0.1</v>
       </c>
-      <c r="C7" s="26" t="s">
-        <v>112</v>
-      </c>
-      <c r="D7" s="26" t="s">
-        <v>112</v>
-      </c>
-      <c r="E7" s="26" t="s">
-        <v>112</v>
-      </c>
-      <c r="F7" s="26" t="s">
-        <v>112</v>
-      </c>
-      <c r="G7" s="26" t="s">
-        <v>112</v>
+      <c r="C7" s="17" t="s">
+        <v>113</v>
+      </c>
+      <c r="D7" s="17" t="s">
+        <v>113</v>
+      </c>
+      <c r="E7" s="17" t="s">
+        <v>113</v>
+      </c>
+      <c r="F7" s="17" t="s">
+        <v>113</v>
+      </c>
+      <c r="G7" s="17" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="25" t="n">
+      <c r="B8" s="29" t="n">
         <v>0.11</v>
       </c>
-      <c r="C8" s="26" t="s">
-        <v>112</v>
-      </c>
-      <c r="D8" s="26" t="s">
-        <v>112</v>
-      </c>
-      <c r="E8" s="26" t="s">
-        <v>112</v>
-      </c>
-      <c r="F8" s="26" t="s">
-        <v>112</v>
-      </c>
-      <c r="G8" s="26" t="s">
-        <v>112</v>
+      <c r="C8" s="17" t="s">
+        <v>113</v>
+      </c>
+      <c r="D8" s="17" t="s">
+        <v>113</v>
+      </c>
+      <c r="E8" s="17" t="s">
+        <v>113</v>
+      </c>
+      <c r="F8" s="17" t="s">
+        <v>113</v>
+      </c>
+      <c r="G8" s="17" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="25" t="n">
+      <c r="B9" s="29" t="n">
         <v>0.12</v>
       </c>
-      <c r="C9" s="26" t="s">
-        <v>112</v>
-      </c>
-      <c r="D9" s="26" t="s">
-        <v>112</v>
-      </c>
-      <c r="E9" s="26" t="s">
-        <v>112</v>
-      </c>
-      <c r="F9" s="26" t="s">
-        <v>112</v>
-      </c>
-      <c r="G9" s="26" t="s">
-        <v>112</v>
+      <c r="C9" s="17" t="s">
+        <v>113</v>
+      </c>
+      <c r="D9" s="17" t="s">
+        <v>113</v>
+      </c>
+      <c r="E9" s="17" t="s">
+        <v>113</v>
+      </c>
+      <c r="F9" s="17" t="s">
+        <v>113</v>
+      </c>
+      <c r="G9" s="17" t="s">
+        <v>113</v>
       </c>
     </row>
   </sheetData>
@@ -2549,107 +2883,107 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A2:F14"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="16"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="1" t="s">
-        <v>113</v>
+      <c r="B2" s="2" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="8"/>
-      <c r="B4" s="8" t="s">
-        <v>114</v>
-      </c>
-      <c r="C4" s="8" t="s">
+      <c r="A4" s="9"/>
+      <c r="B4" s="9" t="s">
         <v>115</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="C4" s="9" t="s">
         <v>116</v>
       </c>
-      <c r="E4" s="8" t="s">
+      <c r="D4" s="9" t="s">
         <v>117</v>
       </c>
-      <c r="F4" s="8" t="s">
+      <c r="E4" s="9" t="s">
         <v>118</v>
       </c>
+      <c r="F4" s="9" t="s">
+        <v>119</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="27"/>
-      <c r="C5" s="27"/>
-      <c r="D5" s="27"/>
-      <c r="E5" s="27"/>
-      <c r="F5" s="27"/>
+      <c r="B5" s="30"/>
+      <c r="C5" s="30"/>
+      <c r="D5" s="30"/>
+      <c r="E5" s="30"/>
+      <c r="F5" s="30"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="27"/>
-      <c r="C6" s="27"/>
-      <c r="D6" s="27"/>
-      <c r="E6" s="27"/>
-      <c r="F6" s="27"/>
+      <c r="B6" s="30"/>
+      <c r="C6" s="30"/>
+      <c r="D6" s="30"/>
+      <c r="E6" s="30"/>
+      <c r="F6" s="30"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="27"/>
-      <c r="C7" s="27"/>
-      <c r="D7" s="27"/>
-      <c r="E7" s="27"/>
-      <c r="F7" s="27"/>
+      <c r="B7" s="30"/>
+      <c r="C7" s="30"/>
+      <c r="D7" s="30"/>
+      <c r="E7" s="30"/>
+      <c r="F7" s="30"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="27"/>
-      <c r="C8" s="27"/>
-      <c r="D8" s="27"/>
-      <c r="E8" s="27"/>
-      <c r="F8" s="27"/>
+      <c r="B8" s="30"/>
+      <c r="C8" s="30"/>
+      <c r="D8" s="30"/>
+      <c r="E8" s="30"/>
+      <c r="F8" s="30"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="27"/>
-      <c r="C9" s="27"/>
-      <c r="D9" s="27"/>
-      <c r="E9" s="27"/>
-      <c r="F9" s="27"/>
+      <c r="B9" s="30"/>
+      <c r="C9" s="30"/>
+      <c r="D9" s="30"/>
+      <c r="E9" s="30"/>
+      <c r="F9" s="30"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="27"/>
-      <c r="C10" s="27"/>
-      <c r="D10" s="27"/>
-      <c r="E10" s="27"/>
-      <c r="F10" s="27"/>
+      <c r="B10" s="30"/>
+      <c r="C10" s="30"/>
+      <c r="D10" s="30"/>
+      <c r="E10" s="30"/>
+      <c r="F10" s="30"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="27"/>
-      <c r="C11" s="27"/>
-      <c r="D11" s="27"/>
-      <c r="E11" s="27"/>
-      <c r="F11" s="27"/>
+      <c r="B11" s="30"/>
+      <c r="C11" s="30"/>
+      <c r="D11" s="30"/>
+      <c r="E11" s="30"/>
+      <c r="F11" s="30"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="27"/>
-      <c r="C12" s="27"/>
-      <c r="D12" s="27"/>
-      <c r="E12" s="27"/>
-      <c r="F12" s="27"/>
+      <c r="B12" s="30"/>
+      <c r="C12" s="30"/>
+      <c r="D12" s="30"/>
+      <c r="E12" s="30"/>
+      <c r="F12" s="30"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="27"/>
-      <c r="C13" s="27"/>
-      <c r="D13" s="27"/>
-      <c r="E13" s="27"/>
-      <c r="F13" s="27"/>
+      <c r="B13" s="30"/>
+      <c r="C13" s="30"/>
+      <c r="D13" s="30"/>
+      <c r="E13" s="30"/>
+      <c r="F13" s="30"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="27"/>
-      <c r="C14" s="27"/>
-      <c r="D14" s="27"/>
-      <c r="E14" s="27"/>
-      <c r="F14" s="27"/>
+      <c r="B14" s="30"/>
+      <c r="C14" s="30"/>
+      <c r="D14" s="30"/>
+      <c r="E14" s="30"/>
+      <c r="F14" s="30"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/12_Equity_Finance/_template_BASE.xlsx
+++ b/12_Equity_Finance/_template_BASE.xlsx
@@ -1,28 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Cover" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Institutional Surface" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Challenge Log" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Lineage Map" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Assumptions" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Cap Table &amp; Dilution" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Rights Offering" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Convertible Securities" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Decision &amp; Checks" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="IS" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="BS" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="CF" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="DCF" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="Comps" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="Sensitivity" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="RefreshLog" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cover" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Institutional Surface" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Challenge Log" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lineage Map" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assumptions" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cap Table &amp; Dilution" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rights Offering" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Convertible Securities" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision &amp; Checks" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IS" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CF" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DCF" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Comps" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sensitivity" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RefreshLog" sheetId="16" state="visible" r:id="rId16"/>
   </sheets>
   <definedNames>
     <definedName name="FS_MODEL_ID">'Institutional Surface'!$C$4</definedName>
@@ -190,6 +190,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="3" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -210,7 +211,6 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="3" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="3" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="3" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -826,19 +826,19 @@
       <c r="C5" s="12" t="n"/>
       <c r="D5" s="12" t="n"/>
       <c r="E5" s="12" t="n"/>
-      <c r="F5" s="12">
+      <c r="F5" s="13">
         <f>E5*(1+Assumptions!C5)</f>
         <v/>
       </c>
-      <c r="G5" s="12">
+      <c r="G5" s="13">
         <f>F5*(1+Assumptions!D5)</f>
         <v/>
       </c>
-      <c r="H5" s="12">
+      <c r="H5" s="13">
         <f>G5*(1+Assumptions!E5)</f>
         <v/>
       </c>
-      <c r="I5" s="12">
+      <c r="I5" s="13">
         <f>H5*(1+Assumptions!F5)</f>
         <v/>
       </c>
@@ -849,28 +849,28 @@
           <t>Revenue growth %</t>
         </is>
       </c>
-      <c r="C6" s="13" t="n"/>
-      <c r="D6" s="13">
+      <c r="C6" s="8" t="n"/>
+      <c r="D6" s="14">
         <f>IFERROR(D5/C5-1,"-")</f>
         <v/>
       </c>
-      <c r="E6" s="13">
+      <c r="E6" s="14">
         <f>IFERROR(E5/D5-1,"-")</f>
         <v/>
       </c>
-      <c r="F6" s="13">
+      <c r="F6" s="14">
         <f>IFERROR(F5/E5-1,"-")</f>
         <v/>
       </c>
-      <c r="G6" s="13">
+      <c r="G6" s="14">
         <f>IFERROR(G5/F5-1,"-")</f>
         <v/>
       </c>
-      <c r="H6" s="13">
+      <c r="H6" s="14">
         <f>IFERROR(H5/G5-1,"-")</f>
         <v/>
       </c>
-      <c r="I6" s="13">
+      <c r="I6" s="14">
         <f>IFERROR(I5/H5-1,"-")</f>
         <v/>
       </c>
@@ -884,19 +884,19 @@
       <c r="C7" s="12" t="n"/>
       <c r="D7" s="12" t="n"/>
       <c r="E7" s="12" t="n"/>
-      <c r="F7" s="12">
+      <c r="F7" s="13">
         <f>F5*(1-Assumptions!C6)</f>
         <v/>
       </c>
-      <c r="G7" s="12">
+      <c r="G7" s="13">
         <f>G5*(1-Assumptions!D6)</f>
         <v/>
       </c>
-      <c r="H7" s="12">
+      <c r="H7" s="13">
         <f>H5*(1-Assumptions!E6)</f>
         <v/>
       </c>
-      <c r="I7" s="12">
+      <c r="I7" s="13">
         <f>I5*(1-Assumptions!F6)</f>
         <v/>
       </c>
@@ -908,27 +908,27 @@
         </is>
       </c>
       <c r="C8" s="12" t="n"/>
-      <c r="D8" s="12">
+      <c r="D8" s="13">
         <f>D5-D7</f>
         <v/>
       </c>
-      <c r="E8" s="12">
+      <c r="E8" s="13">
         <f>E5-E7</f>
         <v/>
       </c>
-      <c r="F8" s="12">
+      <c r="F8" s="13">
         <f>F5-F7</f>
         <v/>
       </c>
-      <c r="G8" s="12">
+      <c r="G8" s="13">
         <f>G5-G7</f>
         <v/>
       </c>
-      <c r="H8" s="12">
+      <c r="H8" s="13">
         <f>H5-H7</f>
         <v/>
       </c>
-      <c r="I8" s="12">
+      <c r="I8" s="13">
         <f>I5-I7</f>
         <v/>
       </c>
@@ -939,28 +939,28 @@
           <t>Gross margin %</t>
         </is>
       </c>
-      <c r="C9" s="13" t="n"/>
-      <c r="D9" s="13">
+      <c r="C9" s="8" t="n"/>
+      <c r="D9" s="14">
         <f>IFERROR(D8/D5,"-")</f>
         <v/>
       </c>
-      <c r="E9" s="13">
+      <c r="E9" s="14">
         <f>IFERROR(E8/E5,"-")</f>
         <v/>
       </c>
-      <c r="F9" s="13">
+      <c r="F9" s="14">
         <f>IFERROR(F8/F5,"-")</f>
         <v/>
       </c>
-      <c r="G9" s="13">
+      <c r="G9" s="14">
         <f>IFERROR(G8/G5,"-")</f>
         <v/>
       </c>
-      <c r="H9" s="13">
+      <c r="H9" s="14">
         <f>IFERROR(H8/H5,"-")</f>
         <v/>
       </c>
-      <c r="I9" s="13">
+      <c r="I9" s="14">
         <f>IFERROR(I8/I5,"-")</f>
         <v/>
       </c>
@@ -974,19 +974,19 @@
       <c r="C10" s="12" t="n"/>
       <c r="D10" s="12" t="n"/>
       <c r="E10" s="12" t="n"/>
-      <c r="F10" s="12">
+      <c r="F10" s="13">
         <f>F5*Assumptions!C7</f>
         <v/>
       </c>
-      <c r="G10" s="12">
+      <c r="G10" s="13">
         <f>G5*Assumptions!D7</f>
         <v/>
       </c>
-      <c r="H10" s="12">
+      <c r="H10" s="13">
         <f>H5*Assumptions!E7</f>
         <v/>
       </c>
-      <c r="I10" s="12">
+      <c r="I10" s="13">
         <f>I5*Assumptions!F7</f>
         <v/>
       </c>
@@ -1000,19 +1000,19 @@
       <c r="C11" s="12" t="n"/>
       <c r="D11" s="12" t="n"/>
       <c r="E11" s="12" t="n"/>
-      <c r="F11" s="12">
+      <c r="F11" s="13">
         <f>F8-F10</f>
         <v/>
       </c>
-      <c r="G11" s="12">
+      <c r="G11" s="13">
         <f>G8-G10</f>
         <v/>
       </c>
-      <c r="H11" s="12">
+      <c r="H11" s="13">
         <f>H8-H10</f>
         <v/>
       </c>
-      <c r="I11" s="12">
+      <c r="I11" s="13">
         <f>I8-I10</f>
         <v/>
       </c>
@@ -1023,22 +1023,22 @@
           <t>EBITDA margin %</t>
         </is>
       </c>
-      <c r="C12" s="13" t="n"/>
-      <c r="D12" s="13" t="n"/>
-      <c r="E12" s="13" t="n"/>
-      <c r="F12" s="13">
+      <c r="C12" s="8" t="n"/>
+      <c r="D12" s="8" t="n"/>
+      <c r="E12" s="8" t="n"/>
+      <c r="F12" s="14">
         <f>IFERROR(F11/F5,"-")</f>
         <v/>
       </c>
-      <c r="G12" s="13">
+      <c r="G12" s="14">
         <f>IFERROR(G11/G5,"-")</f>
         <v/>
       </c>
-      <c r="H12" s="13">
+      <c r="H12" s="14">
         <f>IFERROR(H11/H5,"-")</f>
         <v/>
       </c>
-      <c r="I12" s="13">
+      <c r="I12" s="14">
         <f>IFERROR(I11/I5,"-")</f>
         <v/>
       </c>
@@ -1052,19 +1052,19 @@
       <c r="C13" s="12" t="n"/>
       <c r="D13" s="12" t="n"/>
       <c r="E13" s="12" t="n"/>
-      <c r="F13" s="12">
+      <c r="F13" s="13">
         <f>F5*Assumptions!C10*Assumptions!C9</f>
         <v/>
       </c>
-      <c r="G13" s="12">
+      <c r="G13" s="13">
         <f>G5*Assumptions!D10*Assumptions!D9</f>
         <v/>
       </c>
-      <c r="H13" s="12">
+      <c r="H13" s="13">
         <f>H5*Assumptions!E10*Assumptions!E9</f>
         <v/>
       </c>
-      <c r="I13" s="12">
+      <c r="I13" s="13">
         <f>I5*Assumptions!F10*Assumptions!F9</f>
         <v/>
       </c>
@@ -1078,19 +1078,19 @@
       <c r="C14" s="12" t="n"/>
       <c r="D14" s="12" t="n"/>
       <c r="E14" s="12" t="n"/>
-      <c r="F14" s="12">
+      <c r="F14" s="13">
         <f>F11-F13</f>
         <v/>
       </c>
-      <c r="G14" s="12">
+      <c r="G14" s="13">
         <f>G11-G13</f>
         <v/>
       </c>
-      <c r="H14" s="12">
+      <c r="H14" s="13">
         <f>H11-H13</f>
         <v/>
       </c>
-      <c r="I14" s="12">
+      <c r="I14" s="13">
         <f>I11-I13</f>
         <v/>
       </c>
@@ -1104,19 +1104,19 @@
       <c r="C15" s="12" t="n"/>
       <c r="D15" s="12" t="n"/>
       <c r="E15" s="12" t="n"/>
-      <c r="F15" s="12">
+      <c r="F15" s="13">
         <f>$E$15</f>
         <v/>
       </c>
-      <c r="G15" s="12">
+      <c r="G15" s="13">
         <f>$E$15</f>
         <v/>
       </c>
-      <c r="H15" s="12">
+      <c r="H15" s="13">
         <f>$E$15</f>
         <v/>
       </c>
-      <c r="I15" s="12">
+      <c r="I15" s="13">
         <f>$E$15</f>
         <v/>
       </c>
@@ -1130,19 +1130,19 @@
       <c r="C16" s="12" t="n"/>
       <c r="D16" s="12" t="n"/>
       <c r="E16" s="12" t="n"/>
-      <c r="F16" s="12">
+      <c r="F16" s="13">
         <f>F14-F15</f>
         <v/>
       </c>
-      <c r="G16" s="12">
+      <c r="G16" s="13">
         <f>G14-G15</f>
         <v/>
       </c>
-      <c r="H16" s="12">
+      <c r="H16" s="13">
         <f>H14-H15</f>
         <v/>
       </c>
-      <c r="I16" s="12">
+      <c r="I16" s="13">
         <f>I14-I15</f>
         <v/>
       </c>
@@ -1156,19 +1156,19 @@
       <c r="C17" s="12" t="n"/>
       <c r="D17" s="12" t="n"/>
       <c r="E17" s="12" t="n"/>
-      <c r="F17" s="12">
+      <c r="F17" s="13">
         <f>F16*Assumptions!C8</f>
         <v/>
       </c>
-      <c r="G17" s="12">
+      <c r="G17" s="13">
         <f>G16*Assumptions!D8</f>
         <v/>
       </c>
-      <c r="H17" s="12">
+      <c r="H17" s="13">
         <f>H16*Assumptions!E8</f>
         <v/>
       </c>
-      <c r="I17" s="12">
+      <c r="I17" s="13">
         <f>I16*Assumptions!F8</f>
         <v/>
       </c>
@@ -1182,19 +1182,19 @@
       <c r="C18" s="12" t="n"/>
       <c r="D18" s="12" t="n"/>
       <c r="E18" s="12" t="n"/>
-      <c r="F18" s="12">
+      <c r="F18" s="13">
         <f>F16-F17</f>
         <v/>
       </c>
-      <c r="G18" s="12">
+      <c r="G18" s="13">
         <f>G16-G17</f>
         <v/>
       </c>
-      <c r="H18" s="12">
+      <c r="H18" s="13">
         <f>H16-H17</f>
         <v/>
       </c>
-      <c r="I18" s="12">
+      <c r="I18" s="13">
         <f>I16-I17</f>
         <v/>
       </c>
@@ -1208,19 +1208,19 @@
       <c r="C19" s="12" t="n"/>
       <c r="D19" s="12" t="n"/>
       <c r="E19" s="12" t="n"/>
-      <c r="F19" s="12">
+      <c r="F19" s="13">
         <f>Assumptions!C12</f>
         <v/>
       </c>
-      <c r="G19" s="12">
+      <c r="G19" s="13">
         <f>Assumptions!D12</f>
         <v/>
       </c>
-      <c r="H19" s="12">
+      <c r="H19" s="13">
         <f>Assumptions!E12</f>
         <v/>
       </c>
-      <c r="I19" s="12">
+      <c r="I19" s="13">
         <f>Assumptions!F12</f>
         <v/>
       </c>
@@ -1234,19 +1234,19 @@
       <c r="C20" s="12" t="n"/>
       <c r="D20" s="12" t="n"/>
       <c r="E20" s="12" t="n"/>
-      <c r="F20" s="12">
+      <c r="F20" s="13">
         <f>IFERROR(F18/F19,"-")</f>
         <v/>
       </c>
-      <c r="G20" s="12">
+      <c r="G20" s="13">
         <f>IFERROR(G18/G19,"-")</f>
         <v/>
       </c>
-      <c r="H20" s="12">
+      <c r="H20" s="13">
         <f>IFERROR(H18/H19,"-")</f>
         <v/>
       </c>
-      <c r="I20" s="12">
+      <c r="I20" s="13">
         <f>IFERROR(I18/I19,"-")</f>
         <v/>
       </c>
@@ -1320,11 +1320,11 @@
           <t>Cash &amp; equivalents</t>
         </is>
       </c>
-      <c r="C5" s="12" t="n"/>
-      <c r="D5" s="12" t="n"/>
-      <c r="E5" s="12" t="n"/>
-      <c r="F5" s="12" t="n"/>
-      <c r="G5" s="12" t="n"/>
+      <c r="C5" s="13" t="n"/>
+      <c r="D5" s="13" t="n"/>
+      <c r="E5" s="13" t="n"/>
+      <c r="F5" s="13" t="n"/>
+      <c r="G5" s="13" t="n"/>
     </row>
     <row r="6">
       <c r="B6" s="4" t="inlineStr">
@@ -1332,11 +1332,11 @@
           <t>Accounts receivable</t>
         </is>
       </c>
-      <c r="C6" s="12" t="n"/>
-      <c r="D6" s="12" t="n"/>
-      <c r="E6" s="12" t="n"/>
-      <c r="F6" s="12" t="n"/>
-      <c r="G6" s="12" t="n"/>
+      <c r="C6" s="13" t="n"/>
+      <c r="D6" s="13" t="n"/>
+      <c r="E6" s="13" t="n"/>
+      <c r="F6" s="13" t="n"/>
+      <c r="G6" s="13" t="n"/>
     </row>
     <row r="7">
       <c r="B7" s="4" t="inlineStr">
@@ -1344,11 +1344,11 @@
           <t>Inventory</t>
         </is>
       </c>
-      <c r="C7" s="12" t="n"/>
-      <c r="D7" s="12" t="n"/>
-      <c r="E7" s="12" t="n"/>
-      <c r="F7" s="12" t="n"/>
-      <c r="G7" s="12" t="n"/>
+      <c r="C7" s="13" t="n"/>
+      <c r="D7" s="13" t="n"/>
+      <c r="E7" s="13" t="n"/>
+      <c r="F7" s="13" t="n"/>
+      <c r="G7" s="13" t="n"/>
     </row>
     <row r="8">
       <c r="B8" s="2" t="inlineStr">
@@ -1356,23 +1356,23 @@
           <t>Total current assets</t>
         </is>
       </c>
-      <c r="C8" s="12">
+      <c r="C8" s="13">
         <f>C5+C6+C7</f>
         <v/>
       </c>
-      <c r="D8" s="12">
+      <c r="D8" s="13">
         <f>D5+D6+D7</f>
         <v/>
       </c>
-      <c r="E8" s="12">
+      <c r="E8" s="13">
         <f>E5+E6+E7</f>
         <v/>
       </c>
-      <c r="F8" s="12">
+      <c r="F8" s="13">
         <f>F5+F6+F7</f>
         <v/>
       </c>
-      <c r="G8" s="12">
+      <c r="G8" s="13">
         <f>G5+G6+G7</f>
         <v/>
       </c>
@@ -1383,11 +1383,11 @@
           <t>PP&amp;E net</t>
         </is>
       </c>
-      <c r="C9" s="12" t="n"/>
-      <c r="D9" s="12" t="n"/>
-      <c r="E9" s="12" t="n"/>
-      <c r="F9" s="12" t="n"/>
-      <c r="G9" s="12" t="n"/>
+      <c r="C9" s="13" t="n"/>
+      <c r="D9" s="13" t="n"/>
+      <c r="E9" s="13" t="n"/>
+      <c r="F9" s="13" t="n"/>
+      <c r="G9" s="13" t="n"/>
     </row>
     <row r="10">
       <c r="B10" s="4" t="inlineStr">
@@ -1395,11 +1395,11 @@
           <t>Goodwill &amp; intangibles</t>
         </is>
       </c>
-      <c r="C10" s="12" t="n"/>
-      <c r="D10" s="12" t="n"/>
-      <c r="E10" s="12" t="n"/>
-      <c r="F10" s="12" t="n"/>
-      <c r="G10" s="12" t="n"/>
+      <c r="C10" s="13" t="n"/>
+      <c r="D10" s="13" t="n"/>
+      <c r="E10" s="13" t="n"/>
+      <c r="F10" s="13" t="n"/>
+      <c r="G10" s="13" t="n"/>
     </row>
     <row r="11">
       <c r="B11" s="2" t="inlineStr">
@@ -1407,23 +1407,23 @@
           <t>Total assets</t>
         </is>
       </c>
-      <c r="C11" s="12">
+      <c r="C11" s="13">
         <f>C8+C9+C10</f>
         <v/>
       </c>
-      <c r="D11" s="12">
+      <c r="D11" s="13">
         <f>D8+D9+D10</f>
         <v/>
       </c>
-      <c r="E11" s="12">
+      <c r="E11" s="13">
         <f>E8+E9+E10</f>
         <v/>
       </c>
-      <c r="F11" s="12">
+      <c r="F11" s="13">
         <f>F8+F9+F10</f>
         <v/>
       </c>
-      <c r="G11" s="12">
+      <c r="G11" s="13">
         <f>G8+G9+G10</f>
         <v/>
       </c>
@@ -1434,11 +1434,11 @@
           <t>Accounts payable</t>
         </is>
       </c>
-      <c r="C12" s="12" t="n"/>
-      <c r="D12" s="12" t="n"/>
-      <c r="E12" s="12" t="n"/>
-      <c r="F12" s="12" t="n"/>
-      <c r="G12" s="12" t="n"/>
+      <c r="C12" s="13" t="n"/>
+      <c r="D12" s="13" t="n"/>
+      <c r="E12" s="13" t="n"/>
+      <c r="F12" s="13" t="n"/>
+      <c r="G12" s="13" t="n"/>
     </row>
     <row r="13">
       <c r="B13" s="4" t="inlineStr">
@@ -1446,11 +1446,11 @@
           <t>Debt (current)</t>
         </is>
       </c>
-      <c r="C13" s="12" t="n"/>
-      <c r="D13" s="12" t="n"/>
-      <c r="E13" s="12" t="n"/>
-      <c r="F13" s="12" t="n"/>
-      <c r="G13" s="12" t="n"/>
+      <c r="C13" s="13" t="n"/>
+      <c r="D13" s="13" t="n"/>
+      <c r="E13" s="13" t="n"/>
+      <c r="F13" s="13" t="n"/>
+      <c r="G13" s="13" t="n"/>
     </row>
     <row r="14">
       <c r="B14" s="2" t="inlineStr">
@@ -1458,23 +1458,23 @@
           <t>Total current liabilities</t>
         </is>
       </c>
-      <c r="C14" s="12">
+      <c r="C14" s="13">
         <f>C12+C13</f>
         <v/>
       </c>
-      <c r="D14" s="12">
+      <c r="D14" s="13">
         <f>D12+D13</f>
         <v/>
       </c>
-      <c r="E14" s="12">
+      <c r="E14" s="13">
         <f>E12+E13</f>
         <v/>
       </c>
-      <c r="F14" s="12">
+      <c r="F14" s="13">
         <f>F12+F13</f>
         <v/>
       </c>
-      <c r="G14" s="12">
+      <c r="G14" s="13">
         <f>G12+G13</f>
         <v/>
       </c>
@@ -1485,11 +1485,11 @@
           <t>Long-term debt</t>
         </is>
       </c>
-      <c r="C15" s="12" t="n"/>
-      <c r="D15" s="12" t="n"/>
-      <c r="E15" s="12" t="n"/>
-      <c r="F15" s="12" t="n"/>
-      <c r="G15" s="12" t="n"/>
+      <c r="C15" s="13" t="n"/>
+      <c r="D15" s="13" t="n"/>
+      <c r="E15" s="13" t="n"/>
+      <c r="F15" s="13" t="n"/>
+      <c r="G15" s="13" t="n"/>
     </row>
     <row r="16">
       <c r="B16" s="2" t="inlineStr">
@@ -1497,23 +1497,23 @@
           <t>Total liabilities</t>
         </is>
       </c>
-      <c r="C16" s="12">
+      <c r="C16" s="13">
         <f>C14+C15</f>
         <v/>
       </c>
-      <c r="D16" s="12">
+      <c r="D16" s="13">
         <f>D14+D15</f>
         <v/>
       </c>
-      <c r="E16" s="12">
+      <c r="E16" s="13">
         <f>E14+E15</f>
         <v/>
       </c>
-      <c r="F16" s="12">
+      <c r="F16" s="13">
         <f>F14+F15</f>
         <v/>
       </c>
-      <c r="G16" s="12">
+      <c r="G16" s="13">
         <f>G14+G15</f>
         <v/>
       </c>
@@ -1524,35 +1524,35 @@
           <t>Total equity</t>
         </is>
       </c>
-      <c r="C17" s="12" t="n"/>
-      <c r="D17" s="12" t="n"/>
-      <c r="E17" s="12" t="n"/>
-      <c r="F17" s="12" t="n"/>
-      <c r="G17" s="12" t="n"/>
+      <c r="C17" s="13" t="n"/>
+      <c r="D17" s="13" t="n"/>
+      <c r="E17" s="13" t="n"/>
+      <c r="F17" s="13" t="n"/>
+      <c r="G17" s="13" t="n"/>
     </row>
     <row r="19">
-      <c r="B19" s="14" t="inlineStr">
+      <c r="B19" s="15" t="inlineStr">
         <is>
           <t>Balance check (Total assets - Total liabilities - Total equity, should = 0)</t>
         </is>
       </c>
-      <c r="C19" s="15">
+      <c r="C19" s="16">
         <f>C11-C16-C17</f>
         <v/>
       </c>
-      <c r="D19" s="15">
+      <c r="D19" s="16">
         <f>D11-D16-D17</f>
         <v/>
       </c>
-      <c r="E19" s="15">
+      <c r="E19" s="16">
         <f>E11-E16-E17</f>
         <v/>
       </c>
-      <c r="F19" s="15">
+      <c r="F19" s="16">
         <f>F11-F16-F17</f>
         <v/>
       </c>
-      <c r="G19" s="15">
+      <c r="G19" s="16">
         <f>G11-G16-G17</f>
         <v/>
       </c>
@@ -1626,17 +1626,17 @@
           <t>Net income</t>
         </is>
       </c>
-      <c r="C5" s="12" t="n"/>
-      <c r="D5" s="12" t="n"/>
-      <c r="E5" s="16">
+      <c r="C5" s="13" t="n"/>
+      <c r="D5" s="13" t="n"/>
+      <c r="E5" s="17">
         <f>IS!F18</f>
         <v/>
       </c>
-      <c r="F5" s="16">
+      <c r="F5" s="17">
         <f>IS!G18</f>
         <v/>
       </c>
-      <c r="G5" s="16">
+      <c r="G5" s="17">
         <f>IS!H18</f>
         <v/>
       </c>
@@ -1647,17 +1647,17 @@
           <t>+ D&amp;A</t>
         </is>
       </c>
-      <c r="C6" s="12" t="n"/>
-      <c r="D6" s="12" t="n"/>
-      <c r="E6" s="16">
+      <c r="C6" s="13" t="n"/>
+      <c r="D6" s="13" t="n"/>
+      <c r="E6" s="17">
         <f>IS!F13</f>
         <v/>
       </c>
-      <c r="F6" s="16">
+      <c r="F6" s="17">
         <f>IS!G13</f>
         <v/>
       </c>
-      <c r="G6" s="16">
+      <c r="G6" s="17">
         <f>IS!H13</f>
         <v/>
       </c>
@@ -1668,11 +1668,11 @@
           <t>+/- Change in NWC</t>
         </is>
       </c>
-      <c r="C7" s="12" t="n"/>
-      <c r="D7" s="12" t="n"/>
-      <c r="E7" s="12" t="n"/>
-      <c r="F7" s="12" t="n"/>
-      <c r="G7" s="12" t="n"/>
+      <c r="C7" s="13" t="n"/>
+      <c r="D7" s="13" t="n"/>
+      <c r="E7" s="13" t="n"/>
+      <c r="F7" s="13" t="n"/>
+      <c r="G7" s="13" t="n"/>
     </row>
     <row r="8">
       <c r="B8" s="2" t="inlineStr">
@@ -1680,23 +1680,23 @@
           <t>Cash flow from operations</t>
         </is>
       </c>
-      <c r="C8" s="12">
+      <c r="C8" s="13">
         <f>C5+C6+C7</f>
         <v/>
       </c>
-      <c r="D8" s="12">
+      <c r="D8" s="13">
         <f>D5+D6+D7</f>
         <v/>
       </c>
-      <c r="E8" s="12">
+      <c r="E8" s="13">
         <f>E5+E6+E7</f>
         <v/>
       </c>
-      <c r="F8" s="12">
+      <c r="F8" s="13">
         <f>F5+F6+F7</f>
         <v/>
       </c>
-      <c r="G8" s="12">
+      <c r="G8" s="13">
         <f>G5+G6+G7</f>
         <v/>
       </c>
@@ -1707,11 +1707,11 @@
           <t>Capex</t>
         </is>
       </c>
-      <c r="C9" s="12" t="n"/>
-      <c r="D9" s="12" t="n"/>
-      <c r="E9" s="12" t="n"/>
-      <c r="F9" s="12" t="n"/>
-      <c r="G9" s="12" t="n"/>
+      <c r="C9" s="13" t="n"/>
+      <c r="D9" s="13" t="n"/>
+      <c r="E9" s="13" t="n"/>
+      <c r="F9" s="13" t="n"/>
+      <c r="G9" s="13" t="n"/>
     </row>
     <row r="10">
       <c r="B10" s="2" t="inlineStr">
@@ -1719,23 +1719,23 @@
           <t>Free cash flow</t>
         </is>
       </c>
-      <c r="C10" s="12">
+      <c r="C10" s="13">
         <f>C8+C9</f>
         <v/>
       </c>
-      <c r="D10" s="12">
+      <c r="D10" s="13">
         <f>D8+D9</f>
         <v/>
       </c>
-      <c r="E10" s="12">
+      <c r="E10" s="13">
         <f>E8+E9</f>
         <v/>
       </c>
-      <c r="F10" s="12">
+      <c r="F10" s="13">
         <f>F8+F9</f>
         <v/>
       </c>
-      <c r="G10" s="12">
+      <c r="G10" s="13">
         <f>G8+G9</f>
         <v/>
       </c>
@@ -1746,11 +1746,11 @@
           <t>Debt issuance/(repayment)</t>
         </is>
       </c>
-      <c r="C11" s="12" t="n"/>
-      <c r="D11" s="12" t="n"/>
-      <c r="E11" s="12" t="n"/>
-      <c r="F11" s="12" t="n"/>
-      <c r="G11" s="12" t="n"/>
+      <c r="C11" s="13" t="n"/>
+      <c r="D11" s="13" t="n"/>
+      <c r="E11" s="13" t="n"/>
+      <c r="F11" s="13" t="n"/>
+      <c r="G11" s="13" t="n"/>
     </row>
     <row r="12">
       <c r="B12" s="4" t="inlineStr">
@@ -1758,11 +1758,11 @@
           <t>Dividends/buybacks</t>
         </is>
       </c>
-      <c r="C12" s="12" t="n"/>
-      <c r="D12" s="12" t="n"/>
-      <c r="E12" s="12" t="n"/>
-      <c r="F12" s="12" t="n"/>
-      <c r="G12" s="12" t="n"/>
+      <c r="C12" s="13" t="n"/>
+      <c r="D12" s="13" t="n"/>
+      <c r="E12" s="13" t="n"/>
+      <c r="F12" s="13" t="n"/>
+      <c r="G12" s="13" t="n"/>
     </row>
     <row r="13">
       <c r="B13" s="4" t="inlineStr">
@@ -1770,23 +1770,23 @@
           <t>Net change in cash</t>
         </is>
       </c>
-      <c r="C13" s="12">
+      <c r="C13" s="13">
         <f>C10+C11+C12</f>
         <v/>
       </c>
-      <c r="D13" s="12">
+      <c r="D13" s="13">
         <f>D10+D11+D12</f>
         <v/>
       </c>
-      <c r="E13" s="12">
+      <c r="E13" s="13">
         <f>E10+E11+E12</f>
         <v/>
       </c>
-      <c r="F13" s="12">
+      <c r="F13" s="13">
         <f>F10+F11+F12</f>
         <v/>
       </c>
-      <c r="G13" s="12">
+      <c r="G13" s="13">
         <f>G10+G11+G12</f>
         <v/>
       </c>
@@ -1802,7 +1802,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:I14"/>
+  <dimension ref="B2:I15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1862,23 +1862,23 @@
           <t>Unlevered FCF</t>
         </is>
       </c>
-      <c r="C5" s="17">
+      <c r="C5" s="18">
         <f>IS!F14*(1-Assumptions!C8)+IS!F13-IS!F5*Assumptions!C10</f>
         <v/>
       </c>
-      <c r="D5" s="17">
+      <c r="D5" s="18">
         <f>IS!G14*(1-Assumptions!D8)+IS!G13-IS!G5*Assumptions!D10</f>
         <v/>
       </c>
-      <c r="E5" s="17">
+      <c r="E5" s="18">
         <f>IS!H14*(1-Assumptions!E8)+IS!H13-IS!H5*Assumptions!E10</f>
         <v/>
       </c>
-      <c r="F5" s="17">
+      <c r="F5" s="18">
         <f>IS!I14*(1-Assumptions!F8)+IS!I13-IS!I5*Assumptions!F10</f>
         <v/>
       </c>
-      <c r="G5" s="17">
+      <c r="G5" s="18">
         <f>F5*(1+Assumptions!G5)</f>
         <v/>
       </c>
@@ -1887,7 +1887,7 @@
           <t>WACC</t>
         </is>
       </c>
-      <c r="I5" s="18" t="n">
+      <c r="I5" s="19" t="n">
         <v>0.1</v>
       </c>
     </row>
@@ -1897,23 +1897,23 @@
           <t>Discount factor</t>
         </is>
       </c>
-      <c r="C6" s="19">
+      <c r="C6" s="20">
         <f>1/(1+$I$5)^(1)</f>
         <v/>
       </c>
-      <c r="D6" s="19">
+      <c r="D6" s="20">
         <f>1/(1+$I$5)^(2)</f>
         <v/>
       </c>
-      <c r="E6" s="19">
+      <c r="E6" s="20">
         <f>1/(1+$I$5)^(3)</f>
         <v/>
       </c>
-      <c r="F6" s="19">
+      <c r="F6" s="20">
         <f>1/(1+$I$5)^(4)</f>
         <v/>
       </c>
-      <c r="G6" s="19">
+      <c r="G6" s="20">
         <f>1/(1+$I$5)^(5)</f>
         <v/>
       </c>
@@ -1922,7 +1922,7 @@
           <t>Terminal growth</t>
         </is>
       </c>
-      <c r="I6" s="18" t="n">
+      <c r="I6" s="19" t="n">
         <v>0.025</v>
       </c>
     </row>
@@ -1932,23 +1932,23 @@
           <t>PV of FCF</t>
         </is>
       </c>
-      <c r="C7" s="20">
+      <c r="C7" s="21">
         <f>C5*C6</f>
         <v/>
       </c>
-      <c r="D7" s="20">
+      <c r="D7" s="21">
         <f>D5*D6</f>
         <v/>
       </c>
-      <c r="E7" s="20">
+      <c r="E7" s="21">
         <f>E5*E6</f>
         <v/>
       </c>
-      <c r="F7" s="20">
+      <c r="F7" s="21">
         <f>F5*F6</f>
         <v/>
       </c>
-      <c r="G7" s="20">
+      <c r="G7" s="21">
         <f>G5*G6</f>
         <v/>
       </c>
@@ -1957,7 +1957,7 @@
           <t>Terminal value</t>
         </is>
       </c>
-      <c r="I7" s="20">
+      <c r="I7" s="21">
         <f>G5*(1+I6)/(I5-I6)</f>
         <v/>
       </c>
@@ -1968,7 +1968,7 @@
           <t>PV of terminal value</t>
         </is>
       </c>
-      <c r="I8" s="20">
+      <c r="I8" s="21">
         <f>I7*G6</f>
         <v/>
       </c>
@@ -1979,7 +1979,7 @@
           <t>Sum PV of FCF</t>
         </is>
       </c>
-      <c r="I9" s="20">
+      <c r="I9" s="21">
         <f>SUM(C7:G7)</f>
         <v/>
       </c>
@@ -1990,7 +1990,7 @@
           <t>Enterprise value</t>
         </is>
       </c>
-      <c r="I10" s="21">
+      <c r="I10" s="22">
         <f>I8+I9</f>
         <v/>
       </c>
@@ -2001,7 +2001,7 @@
           <t>Less: net debt</t>
         </is>
       </c>
-      <c r="I11" s="22" t="n">
+      <c r="I11" s="23" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2011,7 +2011,7 @@
           <t>Equity value</t>
         </is>
       </c>
-      <c r="I12" s="21">
+      <c r="I12" s="22">
         <f>I10-I11</f>
         <v/>
       </c>
@@ -2022,7 +2022,7 @@
           <t>Diluted shares (mm)</t>
         </is>
       </c>
-      <c r="I13" s="22" t="n">
+      <c r="I13" s="23" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2032,8 +2032,19 @@
           <t>Implied value/share</t>
         </is>
       </c>
-      <c r="I14" s="21">
-        <f>I12/I13</f>
+      <c r="I14" s="22">
+        <f>IF(OR(IS!E5="",IS!E5=0),"n/a - no forecast base",I12/I13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Forecast base (IS!E5)</t>
+        </is>
+      </c>
+      <c r="I15" s="2">
+        <f>IF(OR(IS!E5="",IS!E5=0),"MISSING - the DCF cannot value anything","present")</f>
         <v/>
       </c>
     </row>
@@ -2121,13 +2132,13 @@
       <c r="E5" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="F5" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" s="23" t="n">
+      <c r="F5" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2146,13 +2157,13 @@
       <c r="E6" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="F6" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" s="23" t="n">
+      <c r="F6" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2171,13 +2182,13 @@
       <c r="E7" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="F7" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" s="23" t="n">
+      <c r="F7" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2196,13 +2207,13 @@
       <c r="E8" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="F8" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" s="23" t="n">
+      <c r="F8" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2221,13 +2232,13 @@
       <c r="E9" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="F9" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" s="23" t="n">
+      <c r="F9" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2246,13 +2257,13 @@
       <c r="E10" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="F10" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" s="23" t="n">
+      <c r="F10" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2271,13 +2282,13 @@
       <c r="E11" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="F11" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" s="23" t="n">
+      <c r="F11" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2287,27 +2298,27 @@
           <t>Median</t>
         </is>
       </c>
-      <c r="C13" s="21">
+      <c r="C13" s="22">
         <f>MEDIAN(C5:C12)</f>
         <v/>
       </c>
-      <c r="D13" s="21">
+      <c r="D13" s="22">
         <f>MEDIAN(D5:D12)</f>
         <v/>
       </c>
-      <c r="E13" s="21">
+      <c r="E13" s="22">
         <f>MEDIAN(E5:E12)</f>
         <v/>
       </c>
-      <c r="F13" s="24">
+      <c r="F13" s="25">
         <f>MEDIAN(F5:F12)</f>
         <v/>
       </c>
-      <c r="G13" s="24">
+      <c r="G13" s="25">
         <f>MEDIAN(G5:G12)</f>
         <v/>
       </c>
-      <c r="H13" s="24">
+      <c r="H13" s="25">
         <f>MEDIAN(H5:H12)</f>
         <v/>
       </c>
@@ -2344,172 +2355,172 @@
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="25" t="inlineStr">
+      <c r="B4" s="26" t="inlineStr">
         <is>
           <t>WACC \ Term. growth</t>
         </is>
       </c>
-      <c r="C4" s="26" t="n">
+      <c r="C4" s="27" t="n">
         <v>0.015</v>
       </c>
-      <c r="D4" s="26" t="n">
+      <c r="D4" s="27" t="n">
         <v>0.02</v>
       </c>
-      <c r="E4" s="26" t="n">
+      <c r="E4" s="27" t="n">
         <v>0.025</v>
       </c>
-      <c r="F4" s="26" t="n">
+      <c r="F4" s="27" t="n">
         <v>0.03</v>
       </c>
-      <c r="G4" s="26" t="n">
+      <c r="G4" s="27" t="n">
         <v>0.035</v>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="26" t="n">
+      <c r="B5" s="27" t="n">
         <v>0.08</v>
       </c>
-      <c r="C5" s="14" t="inlineStr">
+      <c r="C5" s="15" t="inlineStr">
         <is>
           <t>[data table — Excel What-If Analysis]</t>
         </is>
       </c>
-      <c r="D5" s="14" t="inlineStr">
+      <c r="D5" s="15" t="inlineStr">
         <is>
           <t>[data table — Excel What-If Analysis]</t>
         </is>
       </c>
-      <c r="E5" s="14" t="inlineStr">
+      <c r="E5" s="15" t="inlineStr">
         <is>
           <t>[data table — Excel What-If Analysis]</t>
         </is>
       </c>
-      <c r="F5" s="14" t="inlineStr">
+      <c r="F5" s="15" t="inlineStr">
         <is>
           <t>[data table — Excel What-If Analysis]</t>
         </is>
       </c>
-      <c r="G5" s="14" t="inlineStr">
+      <c r="G5" s="15" t="inlineStr">
         <is>
           <t>[data table — Excel What-If Analysis]</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="26" t="n">
+      <c r="B6" s="27" t="n">
         <v>0.09</v>
       </c>
-      <c r="C6" s="14" t="inlineStr">
+      <c r="C6" s="15" t="inlineStr">
         <is>
           <t>[data table — Excel What-If Analysis]</t>
         </is>
       </c>
-      <c r="D6" s="14" t="inlineStr">
+      <c r="D6" s="15" t="inlineStr">
         <is>
           <t>[data table — Excel What-If Analysis]</t>
         </is>
       </c>
-      <c r="E6" s="14" t="inlineStr">
+      <c r="E6" s="15" t="inlineStr">
         <is>
           <t>[data table — Excel What-If Analysis]</t>
         </is>
       </c>
-      <c r="F6" s="14" t="inlineStr">
+      <c r="F6" s="15" t="inlineStr">
         <is>
           <t>[data table — Excel What-If Analysis]</t>
         </is>
       </c>
-      <c r="G6" s="14" t="inlineStr">
+      <c r="G6" s="15" t="inlineStr">
         <is>
           <t>[data table — Excel What-If Analysis]</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="26" t="n">
+      <c r="B7" s="27" t="n">
         <v>0.1</v>
       </c>
-      <c r="C7" s="14" t="inlineStr">
+      <c r="C7" s="15" t="inlineStr">
         <is>
           <t>[data table — Excel What-If Analysis]</t>
         </is>
       </c>
-      <c r="D7" s="14" t="inlineStr">
+      <c r="D7" s="15" t="inlineStr">
         <is>
           <t>[data table — Excel What-If Analysis]</t>
         </is>
       </c>
-      <c r="E7" s="14" t="inlineStr">
+      <c r="E7" s="15" t="inlineStr">
         <is>
           <t>[data table — Excel What-If Analysis]</t>
         </is>
       </c>
-      <c r="F7" s="14" t="inlineStr">
+      <c r="F7" s="15" t="inlineStr">
         <is>
           <t>[data table — Excel What-If Analysis]</t>
         </is>
       </c>
-      <c r="G7" s="14" t="inlineStr">
+      <c r="G7" s="15" t="inlineStr">
         <is>
           <t>[data table — Excel What-If Analysis]</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="26" t="n">
+      <c r="B8" s="27" t="n">
         <v>0.11</v>
       </c>
-      <c r="C8" s="14" t="inlineStr">
+      <c r="C8" s="15" t="inlineStr">
         <is>
           <t>[data table — Excel What-If Analysis]</t>
         </is>
       </c>
-      <c r="D8" s="14" t="inlineStr">
+      <c r="D8" s="15" t="inlineStr">
         <is>
           <t>[data table — Excel What-If Analysis]</t>
         </is>
       </c>
-      <c r="E8" s="14" t="inlineStr">
+      <c r="E8" s="15" t="inlineStr">
         <is>
           <t>[data table — Excel What-If Analysis]</t>
         </is>
       </c>
-      <c r="F8" s="14" t="inlineStr">
+      <c r="F8" s="15" t="inlineStr">
         <is>
           <t>[data table — Excel What-If Analysis]</t>
         </is>
       </c>
-      <c r="G8" s="14" t="inlineStr">
+      <c r="G8" s="15" t="inlineStr">
         <is>
           <t>[data table — Excel What-If Analysis]</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="26" t="n">
+      <c r="B9" s="27" t="n">
         <v>0.12</v>
       </c>
-      <c r="C9" s="14" t="inlineStr">
+      <c r="C9" s="15" t="inlineStr">
         <is>
           <t>[data table — Excel What-If Analysis]</t>
         </is>
       </c>
-      <c r="D9" s="14" t="inlineStr">
+      <c r="D9" s="15" t="inlineStr">
         <is>
           <t>[data table — Excel What-If Analysis]</t>
         </is>
       </c>
-      <c r="E9" s="14" t="inlineStr">
+      <c r="E9" s="15" t="inlineStr">
         <is>
           <t>[data table — Excel What-If Analysis]</t>
         </is>
       </c>
-      <c r="F9" s="14" t="inlineStr">
+      <c r="F9" s="15" t="inlineStr">
         <is>
           <t>[data table — Excel What-If Analysis]</t>
         </is>
       </c>
-      <c r="G9" s="14" t="inlineStr">
+      <c r="G9" s="15" t="inlineStr">
         <is>
           <t>[data table — Excel What-If Analysis]</t>
         </is>
@@ -2573,74 +2584,74 @@
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="27" t="n"/>
-      <c r="C5" s="27" t="n"/>
-      <c r="D5" s="27" t="n"/>
-      <c r="E5" s="27" t="n"/>
-      <c r="F5" s="27" t="n"/>
+      <c r="B5" s="28" t="n"/>
+      <c r="C5" s="28" t="n"/>
+      <c r="D5" s="28" t="n"/>
+      <c r="E5" s="28" t="n"/>
+      <c r="F5" s="28" t="n"/>
     </row>
     <row r="6">
-      <c r="B6" s="27" t="n"/>
-      <c r="C6" s="27" t="n"/>
-      <c r="D6" s="27" t="n"/>
-      <c r="E6" s="27" t="n"/>
-      <c r="F6" s="27" t="n"/>
+      <c r="B6" s="28" t="n"/>
+      <c r="C6" s="28" t="n"/>
+      <c r="D6" s="28" t="n"/>
+      <c r="E6" s="28" t="n"/>
+      <c r="F6" s="28" t="n"/>
     </row>
     <row r="7">
-      <c r="B7" s="27" t="n"/>
-      <c r="C7" s="27" t="n"/>
-      <c r="D7" s="27" t="n"/>
-      <c r="E7" s="27" t="n"/>
-      <c r="F7" s="27" t="n"/>
+      <c r="B7" s="28" t="n"/>
+      <c r="C7" s="28" t="n"/>
+      <c r="D7" s="28" t="n"/>
+      <c r="E7" s="28" t="n"/>
+      <c r="F7" s="28" t="n"/>
     </row>
     <row r="8">
-      <c r="B8" s="27" t="n"/>
-      <c r="C8" s="27" t="n"/>
-      <c r="D8" s="27" t="n"/>
-      <c r="E8" s="27" t="n"/>
-      <c r="F8" s="27" t="n"/>
+      <c r="B8" s="28" t="n"/>
+      <c r="C8" s="28" t="n"/>
+      <c r="D8" s="28" t="n"/>
+      <c r="E8" s="28" t="n"/>
+      <c r="F8" s="28" t="n"/>
     </row>
     <row r="9">
-      <c r="B9" s="27" t="n"/>
-      <c r="C9" s="27" t="n"/>
-      <c r="D9" s="27" t="n"/>
-      <c r="E9" s="27" t="n"/>
-      <c r="F9" s="27" t="n"/>
+      <c r="B9" s="28" t="n"/>
+      <c r="C9" s="28" t="n"/>
+      <c r="D9" s="28" t="n"/>
+      <c r="E9" s="28" t="n"/>
+      <c r="F9" s="28" t="n"/>
     </row>
     <row r="10">
-      <c r="B10" s="27" t="n"/>
-      <c r="C10" s="27" t="n"/>
-      <c r="D10" s="27" t="n"/>
-      <c r="E10" s="27" t="n"/>
-      <c r="F10" s="27" t="n"/>
+      <c r="B10" s="28" t="n"/>
+      <c r="C10" s="28" t="n"/>
+      <c r="D10" s="28" t="n"/>
+      <c r="E10" s="28" t="n"/>
+      <c r="F10" s="28" t="n"/>
     </row>
     <row r="11">
-      <c r="B11" s="27" t="n"/>
-      <c r="C11" s="27" t="n"/>
-      <c r="D11" s="27" t="n"/>
-      <c r="E11" s="27" t="n"/>
-      <c r="F11" s="27" t="n"/>
+      <c r="B11" s="28" t="n"/>
+      <c r="C11" s="28" t="n"/>
+      <c r="D11" s="28" t="n"/>
+      <c r="E11" s="28" t="n"/>
+      <c r="F11" s="28" t="n"/>
     </row>
     <row r="12">
-      <c r="B12" s="27" t="n"/>
-      <c r="C12" s="27" t="n"/>
-      <c r="D12" s="27" t="n"/>
-      <c r="E12" s="27" t="n"/>
-      <c r="F12" s="27" t="n"/>
+      <c r="B12" s="28" t="n"/>
+      <c r="C12" s="28" t="n"/>
+      <c r="D12" s="28" t="n"/>
+      <c r="E12" s="28" t="n"/>
+      <c r="F12" s="28" t="n"/>
     </row>
     <row r="13">
-      <c r="B13" s="27" t="n"/>
-      <c r="C13" s="27" t="n"/>
-      <c r="D13" s="27" t="n"/>
-      <c r="E13" s="27" t="n"/>
-      <c r="F13" s="27" t="n"/>
+      <c r="B13" s="28" t="n"/>
+      <c r="C13" s="28" t="n"/>
+      <c r="D13" s="28" t="n"/>
+      <c r="E13" s="28" t="n"/>
+      <c r="F13" s="28" t="n"/>
     </row>
     <row r="14">
-      <c r="B14" s="27" t="n"/>
-      <c r="C14" s="27" t="n"/>
-      <c r="D14" s="27" t="n"/>
-      <c r="E14" s="27" t="n"/>
-      <c r="F14" s="27" t="n"/>
+      <c r="B14" s="28" t="n"/>
+      <c r="C14" s="28" t="n"/>
+      <c r="D14" s="28" t="n"/>
+      <c r="E14" s="28" t="n"/>
+      <c r="F14" s="28" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4218,23 +4229,23 @@
           <t>Shares outstanding (mm)</t>
         </is>
       </c>
-      <c r="C12" s="28">
+      <c r="C12" s="29">
         <f>'Cap Table &amp; Dilution'!E19</f>
         <v/>
       </c>
-      <c r="D12" s="28">
+      <c r="D12" s="29">
         <f>'Cap Table &amp; Dilution'!E19</f>
         <v/>
       </c>
-      <c r="E12" s="28">
+      <c r="E12" s="29">
         <f>'Cap Table &amp; Dilution'!E19</f>
         <v/>
       </c>
-      <c r="F12" s="28">
+      <c r="F12" s="29">
         <f>'Cap Table &amp; Dilution'!E19</f>
         <v/>
       </c>
-      <c r="G12" s="28">
+      <c r="G12" s="29">
         <f>'Cap Table &amp; Dilution'!E19</f>
         <v/>
       </c>
@@ -4333,7 +4344,7 @@
           <t>Active scenario</t>
         </is>
       </c>
-      <c r="C3" s="29" t="inlineStr">
+      <c r="C3" s="30" t="inlineStr">
         <is>
           <t>Base</t>
         </is>
@@ -4372,13 +4383,13 @@
           <t>Existing common shares</t>
         </is>
       </c>
-      <c r="C5" s="30" t="n">
+      <c r="C5" s="31" t="n">
         <v>100</v>
       </c>
-      <c r="D5" s="30" t="n">
+      <c r="D5" s="31" t="n">
         <v>100</v>
       </c>
-      <c r="E5" s="31">
+      <c r="E5" s="32">
         <f>IF($C$3="Adversarial",D5,C5)</f>
         <v/>
       </c>
@@ -4394,13 +4405,13 @@
           <t>In-the-money options / RSUs</t>
         </is>
       </c>
-      <c r="C6" s="30" t="n">
+      <c r="C6" s="31" t="n">
         <v>5</v>
       </c>
-      <c r="D6" s="30" t="n">
+      <c r="D6" s="31" t="n">
         <v>20</v>
       </c>
-      <c r="E6" s="31">
+      <c r="E6" s="32">
         <f>IF($C$3="Adversarial",D6,C6)</f>
         <v/>
       </c>
@@ -4416,13 +4427,13 @@
           <t>Primary shares issued</t>
         </is>
       </c>
-      <c r="C7" s="30" t="n">
+      <c r="C7" s="31" t="n">
         <v>20</v>
       </c>
-      <c r="D7" s="30" t="n">
+      <c r="D7" s="31" t="n">
         <v>150</v>
       </c>
-      <c r="E7" s="31">
+      <c r="E7" s="32">
         <f>IF($C$3="Adversarial",D7,C7)</f>
         <v/>
       </c>
@@ -4438,13 +4449,13 @@
           <t>Rights shares issued</t>
         </is>
       </c>
-      <c r="C8" s="30" t="n">
+      <c r="C8" s="31" t="n">
         <v>25</v>
       </c>
-      <c r="D8" s="30" t="n">
+      <c r="D8" s="31" t="n">
         <v>100</v>
       </c>
-      <c r="E8" s="31">
+      <c r="E8" s="32">
         <f>IF($C$3="Adversarial",D8,C8)</f>
         <v/>
       </c>
@@ -4460,13 +4471,13 @@
           <t>Convertible principal</t>
         </is>
       </c>
-      <c r="C9" s="32" t="n">
+      <c r="C9" s="12" t="n">
         <v>100</v>
       </c>
-      <c r="D9" s="32" t="n">
+      <c r="D9" s="12" t="n">
         <v>500</v>
       </c>
-      <c r="E9" s="15">
+      <c r="E9" s="16">
         <f>IF($C$3="Adversarial",D9,C9)</f>
         <v/>
       </c>
@@ -4526,13 +4537,13 @@
           <t>Transaction fees</t>
         </is>
       </c>
-      <c r="C12" s="32" t="n">
+      <c r="C12" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="D12" s="32" t="n">
+      <c r="D12" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="E12" s="15">
+      <c r="E12" s="16">
         <f>IF($C$3="Adversarial",D12,C12)</f>
         <v/>
       </c>
@@ -4587,7 +4598,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="25" t="inlineStr">
+      <c r="B17" s="26" t="inlineStr">
         <is>
           <t>Derived outputs</t>
         </is>
@@ -4599,15 +4610,15 @@
           <t>Converted shares</t>
         </is>
       </c>
-      <c r="C18" s="31">
+      <c r="C18" s="32">
         <f>IFERROR(C9/C10,0)</f>
         <v/>
       </c>
-      <c r="D18" s="31">
+      <c r="D18" s="32">
         <f>IFERROR(D9/D10,0)</f>
         <v/>
       </c>
-      <c r="E18" s="31">
+      <c r="E18" s="32">
         <f>IFERROR(E9/E10,0)</f>
         <v/>
       </c>
@@ -4618,15 +4629,15 @@
           <t>Fully diluted post-money shares</t>
         </is>
       </c>
-      <c r="C19" s="31">
+      <c r="C19" s="32">
         <f>SUM(C5:C8)+C18</f>
         <v/>
       </c>
-      <c r="D19" s="31">
+      <c r="D19" s="32">
         <f>SUM(D5:D8)+D18</f>
         <v/>
       </c>
-      <c r="E19" s="31">
+      <c r="E19" s="32">
         <f>SUM(E5:E8)+E18</f>
         <v/>
       </c>
@@ -4694,15 +4705,15 @@
           <t>Gross primary proceeds</t>
         </is>
       </c>
-      <c r="C23" s="15">
+      <c r="C23" s="16">
         <f>C7*C11</f>
         <v/>
       </c>
-      <c r="D23" s="15">
+      <c r="D23" s="16">
         <f>D7*D11</f>
         <v/>
       </c>
-      <c r="E23" s="15">
+      <c r="E23" s="16">
         <f>E7*E11</f>
         <v/>
       </c>
@@ -4713,15 +4724,15 @@
           <t>Net primary proceeds</t>
         </is>
       </c>
-      <c r="C24" s="15">
+      <c r="C24" s="16">
         <f>C23-C12</f>
         <v/>
       </c>
-      <c r="D24" s="15">
+      <c r="D24" s="16">
         <f>D23-D12</f>
         <v/>
       </c>
-      <c r="E24" s="15">
+      <c r="E24" s="16">
         <f>E23-E12</f>
         <v/>
       </c>
@@ -4732,21 +4743,21 @@
           <t>Share-conservation residual</t>
         </is>
       </c>
-      <c r="C25" s="31">
+      <c r="C25" s="32">
         <f>C19-C5-C6-C7-C8-C18</f>
         <v/>
       </c>
-      <c r="D25" s="31">
+      <c r="D25" s="32">
         <f>D19-D5-D6-D7-D8-D18</f>
         <v/>
       </c>
-      <c r="E25" s="31">
+      <c r="E25" s="32">
         <f>E19-E5-E6-E7-E8-E18</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="B27" s="14" t="inlineStr">
+      <c r="B27" s="15" t="inlineStr">
         <is>
           <t>The fully diluted denominator must use the security-specific treasury-stock, if-converted, contingently issuable, and anti-dilution conventions approved for the analysis.</t>
         </is>
@@ -4808,11 +4819,11 @@
           <t>Existing shares entitled</t>
         </is>
       </c>
-      <c r="C5" s="31">
+      <c r="C5" s="32">
         <f>'Cap Table &amp; Dilution'!C5</f>
         <v/>
       </c>
-      <c r="D5" s="31">
+      <c r="D5" s="32">
         <f>'Cap Table &amp; Dilution'!D5</f>
         <v/>
       </c>
@@ -4828,11 +4839,11 @@
           <t>Rights shares offered</t>
         </is>
       </c>
-      <c r="C6" s="31">
+      <c r="C6" s="32">
         <f>'Cap Table &amp; Dilution'!C8</f>
         <v/>
       </c>
-      <c r="D6" s="31">
+      <c r="D6" s="32">
         <f>'Cap Table &amp; Dilution'!D8</f>
         <v/>
       </c>
@@ -4920,11 +4931,11 @@
           <t>Theoretical ex-rights price</t>
         </is>
       </c>
-      <c r="C13" s="15">
+      <c r="C13" s="16">
         <f>IFERROR((C5*C7+C6*C8)/(C5+C6),0)</f>
         <v/>
       </c>
-      <c r="D13" s="15">
+      <c r="D13" s="16">
         <f>IFERROR((D5*D7+D6*D8)/(D5+D6),0)</f>
         <v/>
       </c>
@@ -4935,11 +4946,11 @@
           <t>Theoretical value per right / existing share</t>
         </is>
       </c>
-      <c r="C14" s="15">
+      <c r="C14" s="16">
         <f>C7-C13</f>
         <v/>
       </c>
-      <c r="D14" s="15">
+      <c r="D14" s="16">
         <f>D7-D13</f>
         <v/>
       </c>
@@ -4965,11 +4976,11 @@
           <t>Expected subscribed shares</t>
         </is>
       </c>
-      <c r="C16" s="31">
+      <c r="C16" s="32">
         <f>C6*C9</f>
         <v/>
       </c>
-      <c r="D16" s="31">
+      <c r="D16" s="32">
         <f>D6*D9</f>
         <v/>
       </c>
@@ -4980,11 +4991,11 @@
           <t>Expected gross proceeds</t>
         </is>
       </c>
-      <c r="C17" s="15">
+      <c r="C17" s="16">
         <f>C16*C8</f>
         <v/>
       </c>
-      <c r="D17" s="15">
+      <c r="D17" s="16">
         <f>D16*D8</f>
         <v/>
       </c>
@@ -4995,11 +5006,11 @@
           <t>Expected standby fee</t>
         </is>
       </c>
-      <c r="C18" s="15">
+      <c r="C18" s="16">
         <f>(C6-C16)*C8*C10</f>
         <v/>
       </c>
-      <c r="D18" s="15">
+      <c r="D18" s="16">
         <f>(D6-D16)*D8*D10</f>
         <v/>
       </c>
@@ -5010,17 +5021,17 @@
           <t>Expected net rights proceeds</t>
         </is>
       </c>
-      <c r="C19" s="15">
+      <c r="C19" s="16">
         <f>C17-C18</f>
         <v/>
       </c>
-      <c r="D19" s="15">
+      <c r="D19" s="16">
         <f>D17-D18</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="14" t="inlineStr">
+      <c r="B21" s="15" t="inlineStr">
         <is>
           <t>TERP is a frictionless reference. Actual value depends on trading, eligibility, taxes, participation, backstop terms, execution leakage, and the use of proceeds.</t>
         </is>
@@ -5082,11 +5093,11 @@
           <t>Principal</t>
         </is>
       </c>
-      <c r="C5" s="15">
+      <c r="C5" s="16">
         <f>'Cap Table &amp; Dilution'!C9</f>
         <v/>
       </c>
-      <c r="D5" s="15">
+      <c r="D5" s="16">
         <f>'Cap Table &amp; Dilution'!D9</f>
         <v/>
       </c>
@@ -5212,11 +5223,11 @@
           <t>Contractual converted shares</t>
         </is>
       </c>
-      <c r="C14" s="31">
+      <c r="C14" s="32">
         <f>IFERROR(C5/C6,0)</f>
         <v/>
       </c>
-      <c r="D14" s="31">
+      <c r="D14" s="32">
         <f>IFERROR(D5/D6,0)</f>
         <v/>
       </c>
@@ -5227,11 +5238,11 @@
           <t>Anti-dilution adjusted shares</t>
         </is>
       </c>
-      <c r="C15" s="31">
+      <c r="C15" s="32">
         <f>IFERROR(C5/C11,0)</f>
         <v/>
       </c>
-      <c r="D15" s="31">
+      <c r="D15" s="32">
         <f>IFERROR(D5/D11,0)</f>
         <v/>
       </c>
@@ -5242,11 +5253,11 @@
           <t>Conversion value</t>
         </is>
       </c>
-      <c r="C16" s="15">
+      <c r="C16" s="16">
         <f>C14*C7</f>
         <v/>
       </c>
-      <c r="D16" s="15">
+      <c r="D16" s="16">
         <f>D14*D7</f>
         <v/>
       </c>
@@ -5257,11 +5268,11 @@
           <t>Redemption value</t>
         </is>
       </c>
-      <c r="C17" s="15">
+      <c r="C17" s="16">
         <f>C5*(1+C10)</f>
         <v/>
       </c>
-      <c r="D17" s="15">
+      <c r="D17" s="16">
         <f>D5*(1+D10)</f>
         <v/>
       </c>
@@ -5287,11 +5298,11 @@
           <t>Incremental anti-dilution shares</t>
         </is>
       </c>
-      <c r="C19" s="31">
+      <c r="C19" s="32">
         <f>C15-C14</f>
         <v/>
       </c>
-      <c r="D19" s="31">
+      <c r="D19" s="32">
         <f>D15-D14</f>
         <v/>
       </c>
@@ -5302,17 +5313,17 @@
           <t>Annual cash coupon</t>
         </is>
       </c>
-      <c r="C20" s="15">
+      <c r="C20" s="16">
         <f>C5*C8</f>
         <v/>
       </c>
-      <c r="D20" s="15">
+      <c r="D20" s="16">
         <f>D5*D8</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="B22" s="14" t="inlineStr">
+      <c r="B22" s="15" t="inlineStr">
         <is>
           <t>This sheet models if-converted economics, not the full value of optionality. Call features, soft calls, resets, make-wholes, caps, floors, and settlement elections require explicit terms.</t>
         </is>
@@ -5374,11 +5385,11 @@
           <t>Share-conservation residual</t>
         </is>
       </c>
-      <c r="C5" s="27">
+      <c r="C5" s="28">
         <f>'Cap Table &amp; Dilution'!E25</f>
         <v/>
       </c>
-      <c r="D5" s="27">
+      <c r="D5" s="28">
         <f>IF(ABS(C5)&lt;0.000001,"PASS","FAIL")</f>
         <v/>
       </c>
@@ -5394,11 +5405,11 @@
           <t>Ownership / dilution identity</t>
         </is>
       </c>
-      <c r="C6" s="27">
+      <c r="C6" s="28">
         <f>'Cap Table &amp; Dilution'!E20+'Cap Table &amp; Dilution'!E21-1</f>
         <v/>
       </c>
-      <c r="D6" s="27">
+      <c r="D6" s="28">
         <f>IF(ABS(C6)&lt;0.000001,"PASS","FAIL")</f>
         <v/>
       </c>
@@ -5414,11 +5425,11 @@
           <t>Existing-holder dilution</t>
         </is>
       </c>
-      <c r="C7" s="27">
+      <c r="C7" s="28">
         <f>'Cap Table &amp; Dilution'!E21</f>
         <v/>
       </c>
-      <c r="D7" s="27">
+      <c r="D7" s="28">
         <f>IF(C7&lt;='Cap Table &amp; Dilution'!E13,"PASS","BREACH")</f>
         <v/>
       </c>
@@ -5434,11 +5445,11 @@
           <t>Option / RSU overhang</t>
         </is>
       </c>
-      <c r="C8" s="27">
+      <c r="C8" s="28">
         <f>'Cap Table &amp; Dilution'!E22</f>
         <v/>
       </c>
-      <c r="D8" s="27">
+      <c r="D8" s="28">
         <f>IF(C8&lt;='Cap Table &amp; Dilution'!E14,"PASS","REVIEW")</f>
         <v/>
       </c>
@@ -5454,11 +5465,11 @@
           <t>Net primary proceeds</t>
         </is>
       </c>
-      <c r="C9" s="27">
+      <c r="C9" s="28">
         <f>'Cap Table &amp; Dilution'!E24</f>
         <v/>
       </c>
-      <c r="D9" s="27">
+      <c r="D9" s="28">
         <f>IF(C9&gt;=0,"PASS","BREACH")</f>
         <v/>
       </c>
@@ -5474,11 +5485,11 @@
           <t>Rights TERP residual</t>
         </is>
       </c>
-      <c r="C10" s="27">
+      <c r="C10" s="28">
         <f>'Rights Offering'!C13-(('Rights Offering'!C5*'Rights Offering'!C7+'Rights Offering'!C6*'Rights Offering'!C8)/('Rights Offering'!C5+'Rights Offering'!C6))</f>
         <v/>
       </c>
-      <c r="D10" s="27">
+      <c r="D10" s="28">
         <f>IF(ABS(C10)&lt;0.000001,"PASS","FAIL")</f>
         <v/>
       </c>
@@ -5494,11 +5505,11 @@
           <t>Rights value</t>
         </is>
       </c>
-      <c r="C11" s="27">
+      <c r="C11" s="28">
         <f>'Rights Offering'!C14</f>
         <v/>
       </c>
-      <c r="D11" s="27">
+      <c r="D11" s="28">
         <f>IF(C11&gt;=0,"PASS","REVIEW")</f>
         <v/>
       </c>
@@ -5514,11 +5525,11 @@
           <t>Adversarial rights participation</t>
         </is>
       </c>
-      <c r="C12" s="27">
+      <c r="C12" s="28">
         <f>'Rights Offering'!D9</f>
         <v/>
       </c>
-      <c r="D12" s="27">
+      <c r="D12" s="28">
         <f>IF(C12&gt;=0.75,"PASS",IF(C12&gt;=0.50,"REVIEW","BREACH"))</f>
         <v/>
       </c>
@@ -5534,11 +5545,11 @@
           <t>Converted-share reconciliation</t>
         </is>
       </c>
-      <c r="C13" s="27">
+      <c r="C13" s="28">
         <f>'Convertible Securities'!C14-'Cap Table &amp; Dilution'!C18</f>
         <v/>
       </c>
-      <c r="D13" s="27">
+      <c r="D13" s="28">
         <f>IF(ABS(C13)&lt;0.000001,"PASS","FAIL")</f>
         <v/>
       </c>
@@ -5554,11 +5565,11 @@
           <t>Incremental anti-dilution shares</t>
         </is>
       </c>
-      <c r="C14" s="27">
+      <c r="C14" s="28">
         <f>'Convertible Securities'!D19</f>
         <v/>
       </c>
-      <c r="D14" s="27">
+      <c r="D14" s="28">
         <f>IF(C14&lt;=0,"PASS","REVIEW")</f>
         <v/>
       </c>
@@ -5580,7 +5591,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="25" t="inlineStr">
+      <c r="B18" s="26" t="inlineStr">
         <is>
           <t>Primary decision outputs</t>
         </is>
@@ -5592,7 +5603,7 @@
           <t>Fully diluted shares</t>
         </is>
       </c>
-      <c r="C19" s="31">
+      <c r="C19" s="32">
         <f>'Cap Table &amp; Dilution'!E19</f>
         <v/>
       </c>
@@ -5614,7 +5625,7 @@
           <t>Net primary proceeds</t>
         </is>
       </c>
-      <c r="C21" s="15">
+      <c r="C21" s="16">
         <f>'Cap Table &amp; Dilution'!E24</f>
         <v/>
       </c>
@@ -5636,7 +5647,7 @@
           <t>Expected net rights proceeds</t>
         </is>
       </c>
-      <c r="C23" s="15">
+      <c r="C23" s="16">
         <f>'Rights Offering'!C19</f>
         <v/>
       </c>
@@ -5647,7 +5658,7 @@
           <t>Contractual converted shares</t>
         </is>
       </c>
-      <c r="C24" s="31">
+      <c r="C24" s="32">
         <f>'Convertible Securities'!C14</f>
         <v/>
       </c>
@@ -5658,7 +5669,7 @@
           <t>Adversarial anti-dilution shares</t>
         </is>
       </c>
-      <c r="C25" s="31">
+      <c r="C25" s="32">
         <f>'Convertible Securities'!D15</f>
         <v/>
       </c>
@@ -5669,7 +5680,7 @@
           <t>Adversarial redemption value</t>
         </is>
       </c>
-      <c r="C26" s="15">
+      <c r="C26" s="16">
         <f>'Convertible Securities'!D17</f>
         <v/>
       </c>
